--- a/Y9/spreadsheets/legacy/07_CTG & DIRT/ScreenTime_Cinemas_Student_DIRT.xlsx
+++ b/Y9/spreadsheets/legacy/07_CTG & DIRT/ScreenTime_Cinemas_Student_DIRT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ash/Desktop/Y9 Data Analysis DIRT/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5DFCC04-CDF7-E24B-8211-977902FB7A61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19F9BCD6-66A8-8E4A-8AA6-34F820356B0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="529" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="72">
   <si>
     <t>RIVERSIDE
 Guided analysis</t>
@@ -173,9 +173,6 @@
     <t>TASK 2  Calculate, compare and advise the manager.  About 14 minutes</t>
   </si>
   <si>
-    <t>1. Complete the gold cells using formulas. 2. Read the graph as it fills in. 3. Write your analysis in the blue boxes below.</t>
-  </si>
-  <si>
     <t>Gold = enter a formula. Blue = type your analysis. White data cells are provided.</t>
   </si>
   <si>
@@ -188,9 +185,6 @@
     <t>The chart is ready to use. Its line appears when you complete I16:I23. Check your totals if the shape looks unexpected.</t>
   </si>
   <si>
-    <t>Choose one management question from row 9. Write four connected sentences in your own words. Use at least two figures and their units.</t>
-  </si>
-  <si>
     <t>What is the overall trend, or which day stands out? Mention an exception if it is useful.</t>
   </si>
   <si>
@@ -200,25 +194,13 @@
     <t>Why does this matter to the cinema? Explain a possible effect on its operation.</t>
   </si>
   <si>
-    <t>What should the manager do, and why? How could the cinema check whether it helped?</t>
-  </si>
-  <si>
-    <t>Save your workbook and submit it on Google Classroom. Add a screenshot of your improved analysis to your CTG evidence slide.</t>
-  </si>
-  <si>
     <t>Optional challenge  Only after your analysis is complete</t>
   </si>
   <si>
     <t>Week 8 weekend tickets</t>
   </si>
   <si>
-    <t>Add Saturday and Sunday in Week 8. Use +.</t>
-  </si>
-  <si>
     <t>Week 8 daily average</t>
-  </si>
-  <si>
-    <t>Divide the Week 8 total by 7. Use /.</t>
   </si>
   <si>
     <t>Extend your analysis: What else would the manager need to know before changing staffing or introducing a promotion?</t>
@@ -318,6 +300,121 @@
   <si>
     <t>Remember to save this into your documents and upload to Google Classroom when complete.</t>
   </si>
+  <si>
+    <t>1. Complete the gold cells using formulas. 
+2. Read the graph as it fills in. 
+3. Write your analysis in the blue boxes below.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF13334B"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>The manager asks:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF13334B"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Is performance improving? Which days need more staff and stock? Which quieter days could benefit from a promotion?</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="9" tint="-0.249977111117893"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Green</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF13334B"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> = enter a formula. 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="7" tint="-0.249977111117893"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Blue</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF13334B"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> = type your analysis.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF13334B"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Summary hints</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF13334B"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>: use C16:I24 for MODE, MAX and MIN. For the range, subtract the lowest result from the highest.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF13334B"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Check units</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF13334B"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>: daily averages are tickets per day. Weekly totals are tickets per week. Compare like with like.</t>
+    </r>
+  </si>
+  <si>
+    <t>The chart is ready to use. Its line appears when you complete the weekly totals. Check your totals if the shape looks unexpected.</t>
+  </si>
+  <si>
+    <t>Challenge Task:  Attempt after your analysis is complete</t>
+  </si>
 </sst>
 </file>
 
@@ -328,7 +425,7 @@
     <numFmt numFmtId="165" formatCode="&quot;£&quot;#,##0"/>
     <numFmt numFmtId="166" formatCode="0.0"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -336,13 +433,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF13334B"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -393,8 +483,22 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="7" tint="-0.249977111117893"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="9" tint="-0.249977111117893"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="11">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -449,8 +553,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="8">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -535,11 +651,79 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -547,155 +731,161 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="1" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="7" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="1" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="1" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="1" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="8" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="1" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="1" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1022,7 +1212,7 @@
           <a:lstStyle/>
           <a:p>
             <a:r>
-              <a:rPr sz="1050">
+              <a:rPr lang="en-GB" sz="1050">
                 <a:latin typeface="Arial"/>
                 <a:ea typeface="Arial"/>
                 <a:cs typeface="Arial"/>
@@ -1059,7 +1249,7 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>'2 Parkside'!$A$16:$A$23</c:f>
+              <c:f>'2 Parkside'!$B$17:$B$24</c:f>
               <c:numCache>
                 <c:formatCode>#,##0</c:formatCode>
                 <c:ptCount val="8"/>
@@ -1092,7 +1282,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'2 Parkside'!$I$16:$I$23</c:f>
+              <c:f>'2 Parkside'!$J$17:$J$24</c:f>
               <c:numCache>
                 <c:formatCode>#,##0</c:formatCode>
                 <c:ptCount val="8"/>
@@ -1142,6 +1332,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:r>
+                  <a:rPr lang="en-GB"/>
                   <a:t>Week</a:t>
                 </a:r>
               </a:p>
@@ -1198,6 +1389,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:r>
+                  <a:rPr lang="en-GB"/>
                   <a:t>Tickets</a:t>
                 </a:r>
               </a:p>
@@ -1371,16 +1563,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>177800</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>88900</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>39</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>177800</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>88900</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -1405,20 +1597,25 @@
     </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:oneCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>45938</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>50800</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="3238500" cy="1095375"/>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>546099</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>362705</xdr:rowOff>
+    </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="ef610bfb-6dd0-4635-a0eb-e3982b1c2840">
+        <xdr:cNvPr id="7" name="Picture 6">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000003000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{117160D4-D583-3BE5-C054-6E882F8E31D4}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1433,27 +1630,31 @@
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
+        <a:xfrm>
+          <a:off x="18130738" y="228600"/>
+          <a:ext cx="1211362" cy="1454905"/>
+        </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
-  </xdr:oneCellAnchor>
+  </xdr:twoCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>149411</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>194235</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="971550" cy="1066800"/>
+    <xdr:ext cx="3238500" cy="1095375"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="7be394ca-608e-46ac-a724-2eaa50ac7fcb">
+        <xdr:cNvPr id="8" name="69356073-47ad-44f1-9026-25d4887740db">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000004000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{443782A2-E537-1649-B326-0F5F764EDCF1}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1468,6 +1669,10 @@
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
+        <a:xfrm>
+          <a:off x="821764" y="373529"/>
+          <a:ext cx="3238500" cy="1095375"/>
+        </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
@@ -1716,16 +1921,16 @@
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
-      <c r="F3" s="50" t="s">
+      <c r="F3" s="33" t="s">
         <v>0</v>
       </c>
-      <c r="G3" s="50" t="s">
+      <c r="G3" s="33" t="s">
         <v>0</v>
       </c>
-      <c r="H3" s="50" t="s">
+      <c r="H3" s="33" t="s">
         <v>0</v>
       </c>
-      <c r="I3" s="50" t="s">
+      <c r="I3" s="33" t="s">
         <v>0</v>
       </c>
       <c r="J3" s="2"/>
@@ -1747,16 +1952,16 @@
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
-      <c r="F4" s="50" t="s">
+      <c r="F4" s="33" t="s">
         <v>0</v>
       </c>
-      <c r="G4" s="50" t="s">
+      <c r="G4" s="33" t="s">
         <v>0</v>
       </c>
-      <c r="H4" s="50" t="s">
+      <c r="H4" s="33" t="s">
         <v>0</v>
       </c>
-      <c r="I4" s="50" t="s">
+      <c r="I4" s="33" t="s">
         <v>0</v>
       </c>
       <c r="J4" s="2"/>
@@ -1809,48 +2014,48 @@
       <c r="K6" s="1"/>
     </row>
     <row r="7" spans="2:22" ht="23" customHeight="1">
-      <c r="B7" s="20" t="s">
+      <c r="B7" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C7" s="20" t="s">
+      <c r="C7" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D7" s="21" t="s">
+      <c r="D7" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="E7" s="21" t="s">
+      <c r="E7" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="F7" s="21" t="s">
+      <c r="F7" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="G7" s="21" t="s">
+      <c r="G7" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="H7" s="20" t="s">
+      <c r="H7" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I7" s="20" t="s">
+      <c r="I7" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J7" s="21" t="s">
+      <c r="J7" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="K7" s="21" t="s">
+      <c r="K7" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="M7" s="51" t="s">
-        <v>70</v>
-      </c>
-      <c r="N7" s="51"/>
-      <c r="O7" s="51"/>
-      <c r="P7" s="51"/>
-      <c r="Q7" s="51"/>
-      <c r="R7" s="51"/>
-      <c r="S7" s="51"/>
-      <c r="T7" s="51"/>
-      <c r="U7" s="51"/>
-      <c r="V7" s="51"/>
+      <c r="M7" s="34" t="s">
+        <v>64</v>
+      </c>
+      <c r="N7" s="34"/>
+      <c r="O7" s="34"/>
+      <c r="P7" s="34"/>
+      <c r="Q7" s="34"/>
+      <c r="R7" s="34"/>
+      <c r="S7" s="34"/>
+      <c r="T7" s="34"/>
+      <c r="U7" s="34"/>
+      <c r="V7" s="34"/>
     </row>
     <row r="8" spans="2:22" ht="23" customHeight="1">
       <c r="B8" s="1"/>
@@ -1865,704 +2070,704 @@
       <c r="K8" s="1"/>
     </row>
     <row r="9" spans="2:22" ht="28" customHeight="1">
-      <c r="B9" s="25" t="s">
-        <v>66</v>
-      </c>
-      <c r="C9" s="25" t="s">
+      <c r="B9" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="C9" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="D9" s="25" t="s">
+      <c r="D9" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="E9" s="25" t="s">
+      <c r="E9" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="F9" s="25" t="s">
+      <c r="F9" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="G9" s="25" t="s">
+      <c r="G9" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="H9" s="25" t="s">
+      <c r="H9" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="I9" s="25" t="s">
+      <c r="I9" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="J9" s="25" t="s">
+      <c r="J9" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="K9" s="25" t="s">
+      <c r="K9" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="M9" s="25" t="s">
+      <c r="M9" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="N9" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="O9" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="P9" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q9" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="R9" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="S9" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="T9" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="U9" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="V9" s="8" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="10" spans="2:22" ht="36" customHeight="1">
+      <c r="B10" s="29" t="s">
+        <v>61</v>
+      </c>
+      <c r="C10" s="27" t="s">
+        <v>6</v>
+      </c>
+      <c r="D10" s="27" t="s">
+        <v>6</v>
+      </c>
+      <c r="E10" s="27" t="s">
+        <v>6</v>
+      </c>
+      <c r="F10" s="27" t="s">
+        <v>6</v>
+      </c>
+      <c r="G10" s="27" t="s">
+        <v>6</v>
+      </c>
+      <c r="H10" s="27" t="s">
+        <v>6</v>
+      </c>
+      <c r="I10" s="27" t="s">
+        <v>6</v>
+      </c>
+      <c r="J10" s="27" t="s">
+        <v>6</v>
+      </c>
+      <c r="K10" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="M10" s="21" t="s">
+        <v>56</v>
+      </c>
+      <c r="N10" s="20"/>
+      <c r="O10" s="20"/>
+      <c r="P10" s="20"/>
+      <c r="Q10" s="20"/>
+      <c r="R10" s="20"/>
+      <c r="S10" s="20"/>
+      <c r="T10" s="20"/>
+      <c r="U10" s="20"/>
+      <c r="V10" s="20"/>
+    </row>
+    <row r="11" spans="2:22" ht="32" customHeight="1">
+      <c r="B11" s="29" t="s">
+        <v>62</v>
+      </c>
+      <c r="C11" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="D11" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="E11" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="F11" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="G11" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="H11" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="I11" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="J11" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="K11" s="28" t="s">
+        <v>7</v>
+      </c>
+      <c r="M11" s="20"/>
+      <c r="N11" s="20"/>
+      <c r="O11" s="20"/>
+      <c r="P11" s="20"/>
+      <c r="Q11" s="20"/>
+      <c r="R11" s="20"/>
+      <c r="S11" s="20"/>
+      <c r="T11" s="20"/>
+      <c r="U11" s="20"/>
+      <c r="V11" s="20"/>
+    </row>
+    <row r="12" spans="2:22" ht="30" customHeight="1">
+      <c r="B12" s="29" t="s">
         <v>63</v>
       </c>
-      <c r="N9" s="25" t="s">
-        <v>31</v>
-      </c>
-      <c r="O9" s="25" t="s">
-        <v>31</v>
-      </c>
-      <c r="P9" s="25" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q9" s="25" t="s">
-        <v>31</v>
-      </c>
-      <c r="R9" s="25" t="s">
-        <v>31</v>
-      </c>
-      <c r="S9" s="25" t="s">
-        <v>31</v>
-      </c>
-      <c r="T9" s="25" t="s">
-        <v>31</v>
-      </c>
-      <c r="U9" s="25" t="s">
-        <v>31</v>
-      </c>
-      <c r="V9" s="25" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="10" spans="2:22" ht="36" customHeight="1">
-      <c r="B10" s="46" t="s">
-        <v>67</v>
-      </c>
-      <c r="C10" s="44" t="s">
-        <v>6</v>
-      </c>
-      <c r="D10" s="44" t="s">
-        <v>6</v>
-      </c>
-      <c r="E10" s="44" t="s">
-        <v>6</v>
-      </c>
-      <c r="F10" s="44" t="s">
-        <v>6</v>
-      </c>
-      <c r="G10" s="44" t="s">
-        <v>6</v>
-      </c>
-      <c r="H10" s="44" t="s">
-        <v>6</v>
-      </c>
-      <c r="I10" s="44" t="s">
-        <v>6</v>
-      </c>
-      <c r="J10" s="44" t="s">
-        <v>6</v>
-      </c>
-      <c r="K10" s="45" t="s">
-        <v>6</v>
-      </c>
-      <c r="M10" s="38" t="s">
-        <v>62</v>
-      </c>
-      <c r="N10" s="37"/>
-      <c r="O10" s="37"/>
-      <c r="P10" s="37"/>
-      <c r="Q10" s="37"/>
-      <c r="R10" s="37"/>
-      <c r="S10" s="37"/>
-      <c r="T10" s="37"/>
-      <c r="U10" s="37"/>
-      <c r="V10" s="37"/>
-    </row>
-    <row r="11" spans="2:22" ht="32" customHeight="1">
-      <c r="B11" s="46" t="s">
-        <v>68</v>
-      </c>
-      <c r="C11" s="44" t="s">
-        <v>7</v>
-      </c>
-      <c r="D11" s="44" t="s">
-        <v>7</v>
-      </c>
-      <c r="E11" s="44" t="s">
-        <v>7</v>
-      </c>
-      <c r="F11" s="44" t="s">
-        <v>7</v>
-      </c>
-      <c r="G11" s="44" t="s">
-        <v>7</v>
-      </c>
-      <c r="H11" s="44" t="s">
-        <v>7</v>
-      </c>
-      <c r="I11" s="44" t="s">
-        <v>7</v>
-      </c>
-      <c r="J11" s="44" t="s">
-        <v>7</v>
-      </c>
-      <c r="K11" s="45" t="s">
-        <v>7</v>
-      </c>
-      <c r="M11" s="37"/>
-      <c r="N11" s="37"/>
-      <c r="O11" s="37"/>
-      <c r="P11" s="37"/>
-      <c r="Q11" s="37"/>
-      <c r="R11" s="37"/>
-      <c r="S11" s="37"/>
-      <c r="T11" s="37"/>
-      <c r="U11" s="37"/>
-      <c r="V11" s="37"/>
-    </row>
-    <row r="12" spans="2:22" ht="30" customHeight="1">
-      <c r="B12" s="46" t="s">
-        <v>69</v>
-      </c>
-      <c r="C12" s="44" t="s">
+      <c r="C12" s="27" t="s">
         <v>8</v>
       </c>
-      <c r="D12" s="44" t="s">
+      <c r="D12" s="27" t="s">
         <v>8</v>
       </c>
-      <c r="E12" s="44" t="s">
+      <c r="E12" s="27" t="s">
         <v>8</v>
       </c>
-      <c r="F12" s="44" t="s">
+      <c r="F12" s="27" t="s">
         <v>8</v>
       </c>
-      <c r="G12" s="44" t="s">
+      <c r="G12" s="27" t="s">
         <v>8</v>
       </c>
-      <c r="H12" s="44" t="s">
+      <c r="H12" s="27" t="s">
         <v>8</v>
       </c>
-      <c r="I12" s="44" t="s">
+      <c r="I12" s="27" t="s">
         <v>8</v>
       </c>
-      <c r="J12" s="44" t="s">
+      <c r="J12" s="27" t="s">
         <v>8</v>
       </c>
-      <c r="K12" s="45" t="s">
+      <c r="K12" s="28" t="s">
         <v>8</v>
       </c>
-      <c r="M12" s="37"/>
-      <c r="N12" s="37"/>
-      <c r="O12" s="37"/>
-      <c r="P12" s="37"/>
-      <c r="Q12" s="37"/>
-      <c r="R12" s="37"/>
-      <c r="S12" s="37"/>
-      <c r="T12" s="37"/>
-      <c r="U12" s="37"/>
-      <c r="V12" s="37"/>
+      <c r="M12" s="20"/>
+      <c r="N12" s="20"/>
+      <c r="O12" s="20"/>
+      <c r="P12" s="20"/>
+      <c r="Q12" s="20"/>
+      <c r="R12" s="20"/>
+      <c r="S12" s="20"/>
+      <c r="T12" s="20"/>
+      <c r="U12" s="20"/>
+      <c r="V12" s="20"/>
     </row>
     <row r="13" spans="2:22" ht="23" customHeight="1">
-      <c r="B13" s="43" t="s">
+      <c r="B13" s="26" t="s">
         <v>9</v>
       </c>
-      <c r="C13" s="44" t="s">
+      <c r="C13" s="27" t="s">
         <v>9</v>
       </c>
-      <c r="D13" s="44" t="s">
+      <c r="D13" s="27" t="s">
         <v>9</v>
       </c>
-      <c r="E13" s="44" t="s">
+      <c r="E13" s="27" t="s">
         <v>9</v>
       </c>
-      <c r="F13" s="44" t="s">
+      <c r="F13" s="27" t="s">
         <v>9</v>
       </c>
-      <c r="G13" s="44" t="s">
+      <c r="G13" s="27" t="s">
         <v>9</v>
       </c>
-      <c r="H13" s="44" t="s">
+      <c r="H13" s="27" t="s">
         <v>9</v>
       </c>
-      <c r="I13" s="44" t="s">
+      <c r="I13" s="27" t="s">
         <v>9</v>
       </c>
-      <c r="J13" s="28" t="s">
+      <c r="J13" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="K13" s="29">
+      <c r="K13" s="12">
         <v>8</v>
       </c>
     </row>
     <row r="14" spans="2:22" ht="33" customHeight="1">
-      <c r="B14" s="47"/>
-      <c r="C14" s="48"/>
-      <c r="D14" s="48"/>
-      <c r="E14" s="48"/>
-      <c r="F14" s="48"/>
-      <c r="G14" s="48"/>
-      <c r="H14" s="48"/>
-      <c r="I14" s="48"/>
-      <c r="J14" s="48"/>
-      <c r="K14" s="49"/>
-      <c r="M14" s="39" t="s">
+      <c r="B14" s="30"/>
+      <c r="C14" s="31"/>
+      <c r="D14" s="31"/>
+      <c r="E14" s="31"/>
+      <c r="F14" s="31"/>
+      <c r="G14" s="31"/>
+      <c r="H14" s="31"/>
+      <c r="I14" s="31"/>
+      <c r="J14" s="31"/>
+      <c r="K14" s="32"/>
+      <c r="M14" s="22" t="s">
         <v>32</v>
       </c>
-      <c r="N14" s="39"/>
-      <c r="O14" s="39"/>
-      <c r="P14" s="39"/>
-      <c r="Q14" s="39"/>
-      <c r="R14" s="39"/>
-      <c r="S14" s="39"/>
-      <c r="T14" s="39"/>
-      <c r="U14" s="39"/>
-      <c r="V14" s="39"/>
+      <c r="N14" s="22"/>
+      <c r="O14" s="22"/>
+      <c r="P14" s="22"/>
+      <c r="Q14" s="22"/>
+      <c r="R14" s="22"/>
+      <c r="S14" s="22"/>
+      <c r="T14" s="22"/>
+      <c r="U14" s="22"/>
+      <c r="V14" s="22"/>
     </row>
     <row r="15" spans="2:22" ht="28" customHeight="1">
-      <c r="B15" s="25" t="s">
-        <v>64</v>
-      </c>
-      <c r="C15" s="25" t="s">
+      <c r="B15" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="C15" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="D15" s="25" t="s">
+      <c r="D15" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="E15" s="25" t="s">
+      <c r="E15" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="F15" s="25" t="s">
+      <c r="F15" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="G15" s="25" t="s">
+      <c r="G15" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="H15" s="25" t="s">
+      <c r="H15" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="I15" s="25" t="s">
+      <c r="I15" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="J15" s="25" t="s">
+      <c r="J15" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="K15" s="25" t="s">
+      <c r="K15" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="M15" s="36" t="s">
+      <c r="M15" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="N15" s="36" t="s">
+      <c r="N15" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="O15" s="36" t="s">
+      <c r="O15" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="P15" s="36" t="s">
+      <c r="P15" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="Q15" s="36" t="s">
+      <c r="Q15" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="R15" s="36" t="s">
+      <c r="R15" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="S15" s="36" t="s">
+      <c r="S15" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="T15" s="36" t="s">
+      <c r="T15" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="U15" s="36" t="s">
+      <c r="U15" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="V15" s="36" t="s">
+      <c r="V15" s="19" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="16" spans="2:22" ht="32" customHeight="1">
-      <c r="B16" s="22" t="s">
+      <c r="B16" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C16" s="22" t="s">
+      <c r="C16" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D16" s="22" t="s">
+      <c r="D16" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E16" s="22" t="s">
+      <c r="E16" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="F16" s="22" t="s">
+      <c r="F16" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G16" s="22" t="s">
+      <c r="G16" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="H16" s="22" t="s">
+      <c r="H16" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="I16" s="22" t="s">
+      <c r="I16" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="J16" s="22" t="s">
+      <c r="J16" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="K16" s="22" t="s">
+      <c r="K16" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="M16" s="40" t="s">
+      <c r="M16" s="23" t="s">
         <v>34</v>
       </c>
-      <c r="N16" s="40"/>
-      <c r="O16" s="40"/>
-      <c r="P16" s="40"/>
-      <c r="Q16" s="40"/>
-      <c r="R16" s="40"/>
-      <c r="S16" s="40"/>
-      <c r="T16" s="40"/>
-      <c r="U16" s="40"/>
-      <c r="V16" s="40"/>
+      <c r="N16" s="23"/>
+      <c r="O16" s="23"/>
+      <c r="P16" s="23"/>
+      <c r="Q16" s="23"/>
+      <c r="R16" s="23"/>
+      <c r="S16" s="23"/>
+      <c r="T16" s="23"/>
+      <c r="U16" s="23"/>
+      <c r="V16" s="23"/>
     </row>
     <row r="17" spans="2:22" ht="26" customHeight="1">
-      <c r="B17" s="31">
+      <c r="B17" s="14">
         <v>1</v>
       </c>
-      <c r="C17" s="23">
+      <c r="C17" s="6">
         <v>90</v>
       </c>
-      <c r="D17" s="23">
+      <c r="D17" s="6">
         <v>70</v>
       </c>
-      <c r="E17" s="23">
+      <c r="E17" s="6">
         <v>100</v>
       </c>
-      <c r="F17" s="23">
+      <c r="F17" s="6">
         <v>110</v>
       </c>
-      <c r="G17" s="23">
+      <c r="G17" s="6">
         <v>180</v>
       </c>
-      <c r="H17" s="23">
+      <c r="H17" s="6">
         <v>240</v>
       </c>
-      <c r="I17" s="23">
+      <c r="I17" s="6">
         <v>190</v>
       </c>
-      <c r="J17" s="26">
+      <c r="J17" s="9">
         <f t="shared" ref="J17:J24" si="0">SUM(C17:I17)</f>
         <v>980</v>
       </c>
-      <c r="K17" s="27">
+      <c r="K17" s="10">
         <f t="shared" ref="K17:K24" si="1">J17*$K$13</f>
         <v>7840</v>
       </c>
-      <c r="M17" s="40"/>
-      <c r="N17" s="40"/>
-      <c r="O17" s="40"/>
-      <c r="P17" s="40"/>
-      <c r="Q17" s="40"/>
-      <c r="R17" s="40"/>
-      <c r="S17" s="40"/>
-      <c r="T17" s="40"/>
-      <c r="U17" s="40"/>
-      <c r="V17" s="40"/>
+      <c r="M17" s="23"/>
+      <c r="N17" s="23"/>
+      <c r="O17" s="23"/>
+      <c r="P17" s="23"/>
+      <c r="Q17" s="23"/>
+      <c r="R17" s="23"/>
+      <c r="S17" s="23"/>
+      <c r="T17" s="23"/>
+      <c r="U17" s="23"/>
+      <c r="V17" s="23"/>
     </row>
     <row r="18" spans="2:22" ht="26" customHeight="1">
-      <c r="B18" s="31">
+      <c r="B18" s="14">
         <v>2</v>
       </c>
-      <c r="C18" s="24">
+      <c r="C18" s="7">
         <v>100</v>
       </c>
-      <c r="D18" s="24">
+      <c r="D18" s="7">
         <v>70</v>
       </c>
-      <c r="E18" s="24">
+      <c r="E18" s="7">
         <v>105</v>
       </c>
-      <c r="F18" s="24">
+      <c r="F18" s="7">
         <v>115</v>
       </c>
-      <c r="G18" s="24">
+      <c r="G18" s="7">
         <v>195</v>
       </c>
-      <c r="H18" s="24">
+      <c r="H18" s="7">
         <v>250</v>
       </c>
-      <c r="I18" s="24">
+      <c r="I18" s="7">
         <v>205</v>
       </c>
-      <c r="J18" s="26">
+      <c r="J18" s="9">
         <f t="shared" si="0"/>
         <v>1040</v>
       </c>
-      <c r="K18" s="27">
+      <c r="K18" s="10">
         <f t="shared" si="1"/>
         <v>8320</v>
       </c>
-      <c r="M18" s="40"/>
-      <c r="N18" s="40"/>
-      <c r="O18" s="40"/>
-      <c r="P18" s="40"/>
-      <c r="Q18" s="40"/>
-      <c r="R18" s="40"/>
-      <c r="S18" s="40"/>
-      <c r="T18" s="40"/>
-      <c r="U18" s="40"/>
-      <c r="V18" s="40"/>
+      <c r="M18" s="23"/>
+      <c r="N18" s="23"/>
+      <c r="O18" s="23"/>
+      <c r="P18" s="23"/>
+      <c r="Q18" s="23"/>
+      <c r="R18" s="23"/>
+      <c r="S18" s="23"/>
+      <c r="T18" s="23"/>
+      <c r="U18" s="23"/>
+      <c r="V18" s="23"/>
     </row>
     <row r="19" spans="2:22" ht="26" customHeight="1">
-      <c r="B19" s="31">
+      <c r="B19" s="14">
         <v>3</v>
       </c>
-      <c r="C19" s="23">
+      <c r="C19" s="6">
         <v>110</v>
       </c>
-      <c r="D19" s="23">
+      <c r="D19" s="6">
         <v>70</v>
       </c>
-      <c r="E19" s="23">
+      <c r="E19" s="6">
         <v>115</v>
       </c>
-      <c r="F19" s="23">
+      <c r="F19" s="6">
         <v>125</v>
       </c>
-      <c r="G19" s="23">
+      <c r="G19" s="6">
         <v>210</v>
       </c>
-      <c r="H19" s="23">
+      <c r="H19" s="6">
         <v>270</v>
       </c>
-      <c r="I19" s="23">
+      <c r="I19" s="6">
         <v>220</v>
       </c>
-      <c r="J19" s="26">
+      <c r="J19" s="9">
         <f t="shared" si="0"/>
         <v>1120</v>
       </c>
-      <c r="K19" s="27">
+      <c r="K19" s="10">
         <f t="shared" si="1"/>
         <v>8960</v>
       </c>
     </row>
     <row r="20" spans="2:22" ht="26" customHeight="1">
-      <c r="B20" s="31">
+      <c r="B20" s="14">
         <v>4</v>
       </c>
-      <c r="C20" s="24">
+      <c r="C20" s="7">
         <v>100</v>
       </c>
-      <c r="D20" s="24">
+      <c r="D20" s="7">
         <v>70</v>
       </c>
-      <c r="E20" s="24">
+      <c r="E20" s="7">
         <v>110</v>
       </c>
-      <c r="F20" s="24">
+      <c r="F20" s="7">
         <v>120</v>
       </c>
-      <c r="G20" s="24">
+      <c r="G20" s="7">
         <v>200</v>
       </c>
-      <c r="H20" s="24">
+      <c r="H20" s="7">
         <v>260</v>
       </c>
-      <c r="I20" s="24">
+      <c r="I20" s="7">
         <v>210</v>
       </c>
-      <c r="J20" s="26">
+      <c r="J20" s="9">
         <f t="shared" si="0"/>
         <v>1070</v>
       </c>
-      <c r="K20" s="27">
+      <c r="K20" s="10">
         <f t="shared" si="1"/>
         <v>8560</v>
       </c>
-      <c r="M20" s="39" t="s">
+      <c r="M20" s="22" t="s">
         <v>35</v>
       </c>
-      <c r="N20" s="39"/>
-      <c r="O20" s="39"/>
-      <c r="P20" s="39"/>
-      <c r="Q20" s="39"/>
-      <c r="R20" s="39"/>
-      <c r="S20" s="39"/>
-      <c r="T20" s="39"/>
-      <c r="U20" s="39"/>
-      <c r="V20" s="39"/>
+      <c r="N20" s="22"/>
+      <c r="O20" s="22"/>
+      <c r="P20" s="22"/>
+      <c r="Q20" s="22"/>
+      <c r="R20" s="22"/>
+      <c r="S20" s="22"/>
+      <c r="T20" s="22"/>
+      <c r="U20" s="22"/>
+      <c r="V20" s="22"/>
     </row>
     <row r="21" spans="2:22" ht="26" customHeight="1">
-      <c r="B21" s="31">
+      <c r="B21" s="14">
         <v>5</v>
       </c>
-      <c r="C21" s="23">
+      <c r="C21" s="6">
         <v>120</v>
       </c>
-      <c r="D21" s="23">
+      <c r="D21" s="6">
         <v>70</v>
       </c>
-      <c r="E21" s="23">
+      <c r="E21" s="6">
         <v>120</v>
       </c>
-      <c r="F21" s="23">
+      <c r="F21" s="6">
         <v>135</v>
       </c>
-      <c r="G21" s="23">
+      <c r="G21" s="6">
         <v>230</v>
       </c>
-      <c r="H21" s="23">
+      <c r="H21" s="6">
         <v>285</v>
       </c>
-      <c r="I21" s="23">
+      <c r="I21" s="6">
         <v>240</v>
       </c>
-      <c r="J21" s="26">
+      <c r="J21" s="9">
         <f t="shared" si="0"/>
         <v>1200</v>
       </c>
-      <c r="K21" s="27">
+      <c r="K21" s="10">
         <f t="shared" si="1"/>
         <v>9600</v>
       </c>
-      <c r="M21" s="36" t="s">
+      <c r="M21" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="N21" s="36"/>
-      <c r="O21" s="36"/>
-      <c r="P21" s="36"/>
-      <c r="Q21" s="36"/>
-      <c r="R21" s="36"/>
-      <c r="S21" s="36"/>
-      <c r="T21" s="36"/>
-      <c r="U21" s="36"/>
-      <c r="V21" s="36"/>
+      <c r="N21" s="19"/>
+      <c r="O21" s="19"/>
+      <c r="P21" s="19"/>
+      <c r="Q21" s="19"/>
+      <c r="R21" s="19"/>
+      <c r="S21" s="19"/>
+      <c r="T21" s="19"/>
+      <c r="U21" s="19"/>
+      <c r="V21" s="19"/>
     </row>
     <row r="22" spans="2:22" ht="26" customHeight="1">
-      <c r="B22" s="31">
+      <c r="B22" s="14">
         <v>6</v>
       </c>
-      <c r="C22" s="24">
+      <c r="C22" s="7">
         <v>130</v>
       </c>
-      <c r="D22" s="24">
+      <c r="D22" s="7">
         <v>85</v>
       </c>
-      <c r="E22" s="24">
+      <c r="E22" s="7">
         <v>130</v>
       </c>
-      <c r="F22" s="24">
+      <c r="F22" s="7">
         <v>145</v>
       </c>
-      <c r="G22" s="24">
+      <c r="G22" s="7">
         <v>245</v>
       </c>
-      <c r="H22" s="24">
+      <c r="H22" s="7">
         <v>300</v>
       </c>
-      <c r="I22" s="24">
+      <c r="I22" s="7">
         <v>255</v>
       </c>
-      <c r="J22" s="26">
+      <c r="J22" s="9">
         <f t="shared" si="0"/>
         <v>1290</v>
       </c>
-      <c r="K22" s="27">
+      <c r="K22" s="10">
         <f t="shared" si="1"/>
         <v>10320</v>
       </c>
-      <c r="M22" s="40" t="s">
+      <c r="M22" s="23" t="s">
         <v>34</v>
       </c>
-      <c r="N22" s="40"/>
-      <c r="O22" s="40"/>
-      <c r="P22" s="40"/>
-      <c r="Q22" s="40"/>
-      <c r="R22" s="40"/>
-      <c r="S22" s="40"/>
-      <c r="T22" s="40"/>
-      <c r="U22" s="40"/>
-      <c r="V22" s="40"/>
+      <c r="N22" s="23"/>
+      <c r="O22" s="23"/>
+      <c r="P22" s="23"/>
+      <c r="Q22" s="23"/>
+      <c r="R22" s="23"/>
+      <c r="S22" s="23"/>
+      <c r="T22" s="23"/>
+      <c r="U22" s="23"/>
+      <c r="V22" s="23"/>
     </row>
     <row r="23" spans="2:22" ht="26" customHeight="1">
-      <c r="B23" s="31">
+      <c r="B23" s="14">
         <v>7</v>
       </c>
-      <c r="C23" s="23">
+      <c r="C23" s="6">
         <v>140</v>
       </c>
-      <c r="D23" s="23">
+      <c r="D23" s="6">
         <v>85</v>
       </c>
-      <c r="E23" s="23">
+      <c r="E23" s="6">
         <v>140</v>
       </c>
-      <c r="F23" s="23">
+      <c r="F23" s="6">
         <v>155</v>
       </c>
-      <c r="G23" s="23">
+      <c r="G23" s="6">
         <v>260</v>
       </c>
-      <c r="H23" s="23">
+      <c r="H23" s="6">
         <v>320</v>
       </c>
-      <c r="I23" s="23">
+      <c r="I23" s="6">
         <v>270</v>
       </c>
-      <c r="J23" s="26">
+      <c r="J23" s="9">
         <f t="shared" si="0"/>
         <v>1370</v>
       </c>
-      <c r="K23" s="27">
+      <c r="K23" s="10">
         <f t="shared" si="1"/>
         <v>10960</v>
       </c>
-      <c r="M23" s="40"/>
-      <c r="N23" s="40"/>
-      <c r="O23" s="40"/>
-      <c r="P23" s="40"/>
-      <c r="Q23" s="40"/>
-      <c r="R23" s="40"/>
-      <c r="S23" s="40"/>
-      <c r="T23" s="40"/>
-      <c r="U23" s="40"/>
-      <c r="V23" s="40"/>
+      <c r="M23" s="23"/>
+      <c r="N23" s="23"/>
+      <c r="O23" s="23"/>
+      <c r="P23" s="23"/>
+      <c r="Q23" s="23"/>
+      <c r="R23" s="23"/>
+      <c r="S23" s="23"/>
+      <c r="T23" s="23"/>
+      <c r="U23" s="23"/>
+      <c r="V23" s="23"/>
     </row>
     <row r="24" spans="2:22" ht="26" customHeight="1">
-      <c r="B24" s="31">
+      <c r="B24" s="14">
         <v>8</v>
       </c>
-      <c r="C24" s="24">
+      <c r="C24" s="7">
         <v>150</v>
       </c>
-      <c r="D24" s="24">
+      <c r="D24" s="7">
         <v>90</v>
       </c>
-      <c r="E24" s="24">
+      <c r="E24" s="7">
         <v>145</v>
       </c>
-      <c r="F24" s="24">
+      <c r="F24" s="7">
         <v>165</v>
       </c>
-      <c r="G24" s="24">
+      <c r="G24" s="7">
         <v>280</v>
       </c>
-      <c r="H24" s="24">
+      <c r="H24" s="7">
         <v>340</v>
       </c>
-      <c r="I24" s="24">
+      <c r="I24" s="7">
         <v>290</v>
       </c>
-      <c r="J24" s="26">
+      <c r="J24" s="9">
         <f t="shared" si="0"/>
         <v>1460</v>
       </c>
-      <c r="K24" s="27">
+      <c r="K24" s="10">
         <f t="shared" si="1"/>
         <v>11680</v>
       </c>
-      <c r="M24" s="40"/>
-      <c r="N24" s="40"/>
-      <c r="O24" s="40"/>
-      <c r="P24" s="40"/>
-      <c r="Q24" s="40"/>
-      <c r="R24" s="40"/>
-      <c r="S24" s="40"/>
-      <c r="T24" s="40"/>
-      <c r="U24" s="40"/>
-      <c r="V24" s="40"/>
+      <c r="M24" s="23"/>
+      <c r="N24" s="23"/>
+      <c r="O24" s="23"/>
+      <c r="P24" s="23"/>
+      <c r="Q24" s="23"/>
+      <c r="R24" s="23"/>
+      <c r="S24" s="23"/>
+      <c r="T24" s="23"/>
+      <c r="U24" s="23"/>
+      <c r="V24" s="23"/>
     </row>
     <row r="25" spans="2:22" ht="23" customHeight="1">
       <c r="B25" s="1"/>
@@ -2587,51 +2792,51 @@
       <c r="V25" s="1"/>
     </row>
     <row r="26" spans="2:22" ht="23" customHeight="1">
-      <c r="B26" s="22" t="s">
+      <c r="B26" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C26" s="30">
+      <c r="C26" s="13">
         <f t="shared" ref="C26:I26" si="2">AVERAGE(C17:C24)</f>
         <v>117.5</v>
       </c>
-      <c r="D26" s="30">
+      <c r="D26" s="13">
         <f t="shared" si="2"/>
         <v>76.25</v>
       </c>
-      <c r="E26" s="30">
+      <c r="E26" s="13">
         <f t="shared" si="2"/>
         <v>120.625</v>
       </c>
-      <c r="F26" s="30">
+      <c r="F26" s="13">
         <f t="shared" si="2"/>
         <v>133.75</v>
       </c>
-      <c r="G26" s="30">
+      <c r="G26" s="13">
         <f t="shared" si="2"/>
         <v>225</v>
       </c>
-      <c r="H26" s="30">
+      <c r="H26" s="13">
         <f t="shared" si="2"/>
         <v>283.125</v>
       </c>
-      <c r="I26" s="30">
+      <c r="I26" s="13">
         <f t="shared" si="2"/>
         <v>235</v>
       </c>
       <c r="J26" s="1"/>
       <c r="K26" s="1"/>
-      <c r="M26" s="39" t="s">
+      <c r="M26" s="22" t="s">
         <v>37</v>
       </c>
-      <c r="N26" s="39"/>
-      <c r="O26" s="39"/>
-      <c r="P26" s="39"/>
-      <c r="Q26" s="39"/>
-      <c r="R26" s="39"/>
-      <c r="S26" s="39"/>
-      <c r="T26" s="39"/>
-      <c r="U26" s="39"/>
-      <c r="V26" s="39"/>
+      <c r="N26" s="22"/>
+      <c r="O26" s="22"/>
+      <c r="P26" s="22"/>
+      <c r="Q26" s="22"/>
+      <c r="R26" s="22"/>
+      <c r="S26" s="22"/>
+      <c r="T26" s="22"/>
+      <c r="U26" s="22"/>
+      <c r="V26" s="22"/>
     </row>
     <row r="27" spans="2:22" ht="23" customHeight="1">
       <c r="B27" s="1"/>
@@ -2644,74 +2849,74 @@
       <c r="I27" s="1"/>
       <c r="J27" s="1"/>
       <c r="K27" s="1"/>
-      <c r="M27" s="52" t="s">
+      <c r="M27" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="N27" s="36"/>
-      <c r="O27" s="36"/>
-      <c r="P27" s="36"/>
-      <c r="Q27" s="36"/>
-      <c r="R27" s="36"/>
-      <c r="S27" s="36"/>
-      <c r="T27" s="36"/>
-      <c r="U27" s="36"/>
-      <c r="V27" s="36"/>
+      <c r="N27" s="19"/>
+      <c r="O27" s="19"/>
+      <c r="P27" s="19"/>
+      <c r="Q27" s="19"/>
+      <c r="R27" s="19"/>
+      <c r="S27" s="19"/>
+      <c r="T27" s="19"/>
+      <c r="U27" s="19"/>
+      <c r="V27" s="19"/>
     </row>
     <row r="28" spans="2:22" ht="28" customHeight="1">
-      <c r="B28" s="25" t="s">
-        <v>65</v>
-      </c>
-      <c r="C28" s="25" t="s">
+      <c r="B28" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="C28" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="D28" s="25" t="s">
+      <c r="D28" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="E28" s="25" t="s">
+      <c r="E28" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="F28" s="25" t="s">
+      <c r="F28" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="G28" s="25" t="s">
+      <c r="G28" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="H28" s="25" t="s">
+      <c r="H28" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="I28" s="25" t="s">
+      <c r="I28" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="J28" s="25" t="s">
+      <c r="J28" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="K28" s="25" t="s">
+      <c r="K28" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="M28" s="40" t="s">
+      <c r="M28" s="23" t="s">
         <v>34</v>
       </c>
-      <c r="N28" s="40"/>
-      <c r="O28" s="40"/>
-      <c r="P28" s="40"/>
-      <c r="Q28" s="40"/>
-      <c r="R28" s="40"/>
-      <c r="S28" s="40"/>
-      <c r="T28" s="40"/>
-      <c r="U28" s="40"/>
-      <c r="V28" s="40"/>
+      <c r="N28" s="23"/>
+      <c r="O28" s="23"/>
+      <c r="P28" s="23"/>
+      <c r="Q28" s="23"/>
+      <c r="R28" s="23"/>
+      <c r="S28" s="23"/>
+      <c r="T28" s="23"/>
+      <c r="U28" s="23"/>
+      <c r="V28" s="23"/>
     </row>
     <row r="29" spans="2:22" ht="23" customHeight="1">
-      <c r="B29" s="34" t="s">
+      <c r="B29" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="C29" s="34" t="s">
+      <c r="C29" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="34" t="s">
+      <c r="D29" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="E29" s="35">
+      <c r="E29" s="18">
         <f>SUM(J17:J24)</f>
         <v>9530</v>
       </c>
@@ -2721,28 +2926,28 @@
       <c r="I29" s="1"/>
       <c r="J29" s="1"/>
       <c r="K29" s="1"/>
-      <c r="M29" s="40"/>
-      <c r="N29" s="40"/>
-      <c r="O29" s="40"/>
-      <c r="P29" s="40"/>
-      <c r="Q29" s="40"/>
-      <c r="R29" s="40"/>
-      <c r="S29" s="40"/>
-      <c r="T29" s="40"/>
-      <c r="U29" s="40"/>
-      <c r="V29" s="40"/>
+      <c r="M29" s="23"/>
+      <c r="N29" s="23"/>
+      <c r="O29" s="23"/>
+      <c r="P29" s="23"/>
+      <c r="Q29" s="23"/>
+      <c r="R29" s="23"/>
+      <c r="S29" s="23"/>
+      <c r="T29" s="23"/>
+      <c r="U29" s="23"/>
+      <c r="V29" s="23"/>
     </row>
     <row r="30" spans="2:22" ht="23" customHeight="1">
-      <c r="B30" s="32" t="s">
+      <c r="B30" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="C30" s="32" t="s">
+      <c r="C30" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="D30" s="32" t="s">
+      <c r="D30" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="E30" s="33">
+      <c r="E30" s="16">
         <f>MODE(C17:I24)</f>
         <v>70</v>
       </c>
@@ -2752,28 +2957,28 @@
       <c r="I30" s="1"/>
       <c r="J30" s="1"/>
       <c r="K30" s="1"/>
-      <c r="M30" s="40"/>
-      <c r="N30" s="40"/>
-      <c r="O30" s="40"/>
-      <c r="P30" s="40"/>
-      <c r="Q30" s="40"/>
-      <c r="R30" s="40"/>
-      <c r="S30" s="40"/>
-      <c r="T30" s="40"/>
-      <c r="U30" s="40"/>
-      <c r="V30" s="40"/>
+      <c r="M30" s="23"/>
+      <c r="N30" s="23"/>
+      <c r="O30" s="23"/>
+      <c r="P30" s="23"/>
+      <c r="Q30" s="23"/>
+      <c r="R30" s="23"/>
+      <c r="S30" s="23"/>
+      <c r="T30" s="23"/>
+      <c r="U30" s="23"/>
+      <c r="V30" s="23"/>
     </row>
     <row r="31" spans="2:22" ht="23" customHeight="1">
-      <c r="B31" s="32" t="s">
+      <c r="B31" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="C31" s="32" t="s">
+      <c r="C31" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="D31" s="32" t="s">
+      <c r="D31" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="E31" s="33">
+      <c r="E31" s="16">
         <f>MAX(C17:I24)</f>
         <v>340</v>
       </c>
@@ -2785,16 +2990,16 @@
       <c r="K31" s="1"/>
     </row>
     <row r="32" spans="2:22" ht="23" customHeight="1">
-      <c r="B32" s="32" t="s">
+      <c r="B32" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="C32" s="32" t="s">
+      <c r="C32" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="32" t="s">
+      <c r="D32" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="E32" s="33">
+      <c r="E32" s="16">
         <f>MIN(C17:I24)</f>
         <v>70</v>
       </c>
@@ -2804,30 +3009,30 @@
       <c r="I32" s="1"/>
       <c r="J32" s="1"/>
       <c r="K32" s="1"/>
-      <c r="M32" s="39" t="s">
+      <c r="M32" s="22" t="s">
         <v>39</v>
       </c>
-      <c r="N32" s="39"/>
-      <c r="O32" s="39"/>
-      <c r="P32" s="39"/>
-      <c r="Q32" s="39"/>
-      <c r="R32" s="39"/>
-      <c r="S32" s="39"/>
-      <c r="T32" s="39"/>
-      <c r="U32" s="39"/>
-      <c r="V32" s="39"/>
+      <c r="N32" s="22"/>
+      <c r="O32" s="22"/>
+      <c r="P32" s="22"/>
+      <c r="Q32" s="22"/>
+      <c r="R32" s="22"/>
+      <c r="S32" s="22"/>
+      <c r="T32" s="22"/>
+      <c r="U32" s="22"/>
+      <c r="V32" s="22"/>
     </row>
     <row r="33" spans="2:22" ht="23" customHeight="1">
-      <c r="B33" s="32" t="s">
+      <c r="B33" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="C33" s="32" t="s">
+      <c r="C33" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="32" t="s">
+      <c r="D33" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="E33" s="33">
+      <c r="E33" s="16">
         <f>E31-E32</f>
         <v>270</v>
       </c>
@@ -2837,18 +3042,18 @@
       <c r="I33" s="1"/>
       <c r="J33" s="1"/>
       <c r="K33" s="1"/>
-      <c r="M33" s="36" t="s">
+      <c r="M33" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="N33" s="36"/>
-      <c r="O33" s="36"/>
-      <c r="P33" s="36"/>
-      <c r="Q33" s="36"/>
-      <c r="R33" s="36"/>
-      <c r="S33" s="36"/>
-      <c r="T33" s="36"/>
-      <c r="U33" s="36"/>
-      <c r="V33" s="36"/>
+      <c r="N33" s="19"/>
+      <c r="O33" s="19"/>
+      <c r="P33" s="19"/>
+      <c r="Q33" s="19"/>
+      <c r="R33" s="19"/>
+      <c r="S33" s="19"/>
+      <c r="T33" s="19"/>
+      <c r="U33" s="19"/>
+      <c r="V33" s="19"/>
     </row>
     <row r="34" spans="2:22" ht="23" customHeight="1">
       <c r="B34" s="1"/>
@@ -2861,30 +3066,30 @@
       <c r="I34" s="1"/>
       <c r="J34" s="1"/>
       <c r="K34" s="1"/>
-      <c r="M34" s="40" t="s">
+      <c r="M34" s="23" t="s">
         <v>34</v>
       </c>
-      <c r="N34" s="40"/>
-      <c r="O34" s="40"/>
-      <c r="P34" s="40"/>
-      <c r="Q34" s="40"/>
-      <c r="R34" s="40"/>
-      <c r="S34" s="40"/>
-      <c r="T34" s="40"/>
-      <c r="U34" s="40"/>
-      <c r="V34" s="40"/>
+      <c r="N34" s="23"/>
+      <c r="O34" s="23"/>
+      <c r="P34" s="23"/>
+      <c r="Q34" s="23"/>
+      <c r="R34" s="23"/>
+      <c r="S34" s="23"/>
+      <c r="T34" s="23"/>
+      <c r="U34" s="23"/>
+      <c r="V34" s="23"/>
     </row>
     <row r="35" spans="2:22" ht="23" customHeight="1">
-      <c r="B35" s="37" t="s">
+      <c r="B35" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="C35" s="37" t="s">
+      <c r="C35" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="D35" s="37" t="s">
+      <c r="D35" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="E35" s="37" t="s">
+      <c r="E35" s="20" t="s">
         <v>29</v>
       </c>
       <c r="F35" s="1"/>
@@ -2893,28 +3098,28 @@
       <c r="I35" s="1"/>
       <c r="J35" s="1"/>
       <c r="K35" s="1"/>
-      <c r="M35" s="40"/>
-      <c r="N35" s="40"/>
-      <c r="O35" s="40"/>
-      <c r="P35" s="40"/>
-      <c r="Q35" s="40"/>
-      <c r="R35" s="40"/>
-      <c r="S35" s="40"/>
-      <c r="T35" s="40"/>
-      <c r="U35" s="40"/>
-      <c r="V35" s="40"/>
+      <c r="M35" s="23"/>
+      <c r="N35" s="23"/>
+      <c r="O35" s="23"/>
+      <c r="P35" s="23"/>
+      <c r="Q35" s="23"/>
+      <c r="R35" s="23"/>
+      <c r="S35" s="23"/>
+      <c r="T35" s="23"/>
+      <c r="U35" s="23"/>
+      <c r="V35" s="23"/>
     </row>
     <row r="36" spans="2:22" ht="23" customHeight="1">
-      <c r="B36" s="37" t="s">
+      <c r="B36" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="C36" s="37" t="s">
+      <c r="C36" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="D36" s="37" t="s">
+      <c r="D36" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="E36" s="37" t="s">
+      <c r="E36" s="20" t="s">
         <v>29</v>
       </c>
       <c r="F36" s="1"/>
@@ -2923,16 +3128,16 @@
       <c r="I36" s="1"/>
       <c r="J36" s="1"/>
       <c r="K36" s="1"/>
-      <c r="M36" s="40"/>
-      <c r="N36" s="40"/>
-      <c r="O36" s="40"/>
-      <c r="P36" s="40"/>
-      <c r="Q36" s="40"/>
-      <c r="R36" s="40"/>
-      <c r="S36" s="40"/>
-      <c r="T36" s="40"/>
-      <c r="U36" s="40"/>
-      <c r="V36" s="40"/>
+      <c r="M36" s="23"/>
+      <c r="N36" s="23"/>
+      <c r="O36" s="23"/>
+      <c r="P36" s="23"/>
+      <c r="Q36" s="23"/>
+      <c r="R36" s="23"/>
+      <c r="S36" s="23"/>
+      <c r="T36" s="23"/>
+      <c r="U36" s="23"/>
+      <c r="V36" s="23"/>
     </row>
     <row r="37" spans="2:22" ht="23" customHeight="1">
       <c r="B37" s="1"/>
@@ -2947,16 +3152,16 @@
       <c r="K37" s="1"/>
     </row>
     <row r="38" spans="2:22" ht="23" customHeight="1">
-      <c r="B38" s="37" t="s">
+      <c r="B38" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="C38" s="37" t="s">
+      <c r="C38" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="D38" s="37" t="s">
+      <c r="D38" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="E38" s="37" t="s">
+      <c r="E38" s="20" t="s">
         <v>30</v>
       </c>
       <c r="F38" s="1"/>
@@ -2965,30 +3170,30 @@
       <c r="I38" s="1"/>
       <c r="J38" s="1"/>
       <c r="K38" s="1"/>
-      <c r="M38" s="41" t="s">
+      <c r="M38" s="24" t="s">
         <v>41</v>
       </c>
-      <c r="N38" s="41"/>
-      <c r="O38" s="41"/>
-      <c r="P38" s="41"/>
-      <c r="Q38" s="41"/>
-      <c r="R38" s="41"/>
-      <c r="S38" s="41"/>
-      <c r="T38" s="41"/>
-      <c r="U38" s="41"/>
-      <c r="V38" s="41"/>
+      <c r="N38" s="24"/>
+      <c r="O38" s="24"/>
+      <c r="P38" s="24"/>
+      <c r="Q38" s="24"/>
+      <c r="R38" s="24"/>
+      <c r="S38" s="24"/>
+      <c r="T38" s="24"/>
+      <c r="U38" s="24"/>
+      <c r="V38" s="24"/>
     </row>
     <row r="39" spans="2:22" ht="23" customHeight="1">
-      <c r="B39" s="37" t="s">
+      <c r="B39" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="C39" s="37" t="s">
+      <c r="C39" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="D39" s="37" t="s">
+      <c r="D39" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="E39" s="37" t="s">
+      <c r="E39" s="20" t="s">
         <v>30</v>
       </c>
       <c r="F39" s="1"/>
@@ -2997,30 +3202,30 @@
       <c r="I39" s="1"/>
       <c r="J39" s="1"/>
       <c r="K39" s="1"/>
-      <c r="M39" s="42" t="s">
+      <c r="M39" s="25" t="s">
         <v>42</v>
       </c>
-      <c r="N39" s="42"/>
-      <c r="O39" s="42"/>
-      <c r="P39" s="42"/>
-      <c r="Q39" s="42"/>
-      <c r="R39" s="42"/>
-      <c r="S39" s="42"/>
-      <c r="T39" s="42"/>
-      <c r="U39" s="42"/>
-      <c r="V39" s="42"/>
+      <c r="N39" s="25"/>
+      <c r="O39" s="25"/>
+      <c r="P39" s="25"/>
+      <c r="Q39" s="25"/>
+      <c r="R39" s="25"/>
+      <c r="S39" s="25"/>
+      <c r="T39" s="25"/>
+      <c r="U39" s="25"/>
+      <c r="V39" s="25"/>
     </row>
     <row r="40" spans="2:22" ht="23" customHeight="1">
-      <c r="B40" s="37" t="s">
+      <c r="B40" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="C40" s="37" t="s">
+      <c r="C40" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="D40" s="37" t="s">
+      <c r="D40" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="E40" s="37" t="s">
+      <c r="E40" s="20" t="s">
         <v>30</v>
       </c>
       <c r="F40" s="1"/>
@@ -3260,1236 +3465,1543 @@
   <sheetPr>
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
-  <dimension ref="A1:J76"/>
+  <dimension ref="B2:V56"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="18" customWidth="1"/>
-    <col min="2" max="8" width="13" customWidth="1"/>
-    <col min="9" max="10" width="18" customWidth="1"/>
+    <col min="1" max="1" width="6.33203125" customWidth="1"/>
+    <col min="2" max="11" width="14.83203125" customWidth="1"/>
+    <col min="13" max="22" width="9.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="30" customHeight="1">
-      <c r="A1" s="2"/>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-    </row>
-    <row r="2" spans="1:10" ht="30" customHeight="1">
-      <c r="A2" s="2"/>
+    <row r="2" spans="2:22" ht="30" customHeight="1">
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
-      <c r="E2" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="F2" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="G2" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="H2" s="12" t="s">
-        <v>43</v>
-      </c>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
       <c r="I2" s="2"/>
       <c r="J2" s="2"/>
-    </row>
-    <row r="3" spans="1:10" ht="30" customHeight="1">
-      <c r="A3" s="2"/>
+      <c r="K2" s="2"/>
+      <c r="L2" s="2"/>
+      <c r="M2" s="2"/>
+      <c r="N2" s="2"/>
+      <c r="O2" s="2"/>
+      <c r="P2" s="2"/>
+      <c r="Q2" s="2"/>
+      <c r="R2" s="2"/>
+      <c r="S2" s="2"/>
+      <c r="T2" s="2"/>
+      <c r="U2" s="2"/>
+      <c r="V2" s="2"/>
+    </row>
+    <row r="3" spans="2:22" ht="30" customHeight="1">
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
-      <c r="E3" s="12" t="s">
+      <c r="E3" s="2"/>
+      <c r="F3" s="33" t="s">
         <v>43</v>
       </c>
-      <c r="F3" s="12" t="s">
+      <c r="G3" s="33" t="s">
         <v>43</v>
       </c>
-      <c r="G3" s="12" t="s">
+      <c r="H3" s="33" t="s">
         <v>43</v>
       </c>
-      <c r="H3" s="12" t="s">
+      <c r="I3" s="33" t="s">
         <v>43</v>
       </c>
-      <c r="I3" s="2"/>
       <c r="J3" s="2"/>
-    </row>
-    <row r="4" spans="1:10" ht="30" customHeight="1">
-      <c r="A4" s="2"/>
+      <c r="K3" s="2"/>
+      <c r="L3" s="2"/>
+      <c r="M3" s="2"/>
+      <c r="N3" s="2"/>
+      <c r="O3" s="2"/>
+      <c r="P3" s="2"/>
+      <c r="Q3" s="2"/>
+      <c r="R3" s="2"/>
+      <c r="S3" s="2"/>
+      <c r="T3" s="2"/>
+      <c r="U3" s="2"/>
+      <c r="V3" s="2"/>
+    </row>
+    <row r="4" spans="2:22" ht="30" customHeight="1">
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
-      <c r="I4" s="2"/>
+      <c r="F4" s="33" t="s">
+        <v>43</v>
+      </c>
+      <c r="G4" s="33" t="s">
+        <v>43</v>
+      </c>
+      <c r="H4" s="33" t="s">
+        <v>43</v>
+      </c>
+      <c r="I4" s="33" t="s">
+        <v>43</v>
+      </c>
       <c r="J4" s="2"/>
-    </row>
-    <row r="5" spans="1:10" ht="23" customHeight="1">
-      <c r="A5" s="1"/>
-      <c r="B5" s="1"/>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
-      <c r="H5" s="1"/>
-      <c r="I5" s="1"/>
-      <c r="J5" s="1"/>
-    </row>
-    <row r="6" spans="1:10" ht="23" customHeight="1">
-      <c r="A6" s="13" t="s">
+      <c r="K4" s="2"/>
+      <c r="L4" s="2"/>
+      <c r="M4" s="2"/>
+      <c r="N4" s="2"/>
+      <c r="O4" s="2"/>
+      <c r="P4" s="2"/>
+      <c r="Q4" s="2"/>
+      <c r="R4" s="2"/>
+      <c r="S4" s="2"/>
+      <c r="T4" s="2"/>
+      <c r="U4" s="2"/>
+      <c r="V4" s="2"/>
+    </row>
+    <row r="5" spans="2:22" ht="30" customHeight="1">
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2"/>
+      <c r="J5" s="2"/>
+      <c r="K5" s="2"/>
+      <c r="L5" s="2"/>
+      <c r="M5" s="2"/>
+      <c r="N5" s="2"/>
+      <c r="O5" s="2"/>
+      <c r="P5" s="2"/>
+      <c r="Q5" s="2"/>
+      <c r="R5" s="2"/>
+      <c r="S5" s="2"/>
+      <c r="T5" s="2"/>
+      <c r="U5" s="2"/>
+      <c r="V5" s="2"/>
+    </row>
+    <row r="6" spans="2:22" ht="23" customHeight="1">
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="1"/>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1"/>
+    </row>
+    <row r="7" spans="2:22" ht="23" customHeight="1">
+      <c r="B7" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="13" t="s">
+      <c r="C7" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C6" s="14" t="s">
+      <c r="D7" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="14" t="s">
+      <c r="E7" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="14" t="s">
+      <c r="F7" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="F6" s="14" t="s">
+      <c r="G7" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="G6" s="13" t="s">
+      <c r="H7" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H6" s="13" t="s">
+      <c r="I7" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="14" t="s">
+      <c r="J7" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="J6" s="14" t="s">
+      <c r="K7" s="4" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="7" spans="1:10" ht="23" customHeight="1">
-      <c r="A7" s="1"/>
-      <c r="B7" s="1"/>
-      <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
-      <c r="E7" s="1"/>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1"/>
-      <c r="H7" s="1"/>
-      <c r="I7" s="1"/>
-      <c r="J7" s="1"/>
-    </row>
-    <row r="8" spans="1:10" ht="28" customHeight="1">
-      <c r="A8" s="15" t="s">
+      <c r="M7" s="34" t="s">
+        <v>64</v>
+      </c>
+      <c r="N7" s="34"/>
+      <c r="O7" s="34"/>
+      <c r="P7" s="34"/>
+      <c r="Q7" s="34"/>
+      <c r="R7" s="34"/>
+      <c r="S7" s="34"/>
+      <c r="T7" s="34"/>
+      <c r="U7" s="34"/>
+      <c r="V7" s="34"/>
+    </row>
+    <row r="8" spans="2:22" ht="23" customHeight="1">
+      <c r="B8" s="1"/>
+      <c r="C8" s="1"/>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1"/>
+      <c r="I8" s="1"/>
+      <c r="J8" s="1"/>
+      <c r="K8" s="1"/>
+    </row>
+    <row r="9" spans="2:22" ht="28" customHeight="1">
+      <c r="B9" s="41" t="s">
         <v>44</v>
       </c>
-      <c r="B8" s="15" t="s">
+      <c r="C9" s="42" t="s">
         <v>44</v>
       </c>
-      <c r="C8" s="15" t="s">
+      <c r="D9" s="42" t="s">
         <v>44</v>
       </c>
-      <c r="D8" s="15" t="s">
+      <c r="E9" s="42" t="s">
         <v>44</v>
       </c>
-      <c r="E8" s="15" t="s">
+      <c r="F9" s="42" t="s">
         <v>44</v>
       </c>
-      <c r="F8" s="15" t="s">
+      <c r="G9" s="42" t="s">
         <v>44</v>
       </c>
-      <c r="G8" s="15" t="s">
+      <c r="H9" s="42" t="s">
         <v>44</v>
       </c>
-      <c r="H8" s="15" t="s">
+      <c r="I9" s="42" t="s">
         <v>44</v>
       </c>
-      <c r="I8" s="15" t="s">
+      <c r="J9" s="42" t="s">
         <v>44</v>
       </c>
-      <c r="J8" s="15" t="s">
+      <c r="K9" s="43" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="9" spans="1:10" ht="36" customHeight="1">
-      <c r="A9" s="16" t="s">
+      <c r="M9" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="N9" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="O9" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="P9" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q9" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="R9" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="S9" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="T9" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="U9" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="V9" s="8" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="10" spans="2:22" ht="36" customHeight="1">
+      <c r="B10" s="38" t="s">
+        <v>66</v>
+      </c>
+      <c r="C10" s="39" t="s">
         <v>6</v>
       </c>
-      <c r="B9" s="16" t="s">
+      <c r="D10" s="39" t="s">
         <v>6</v>
       </c>
-      <c r="C9" s="16" t="s">
+      <c r="E10" s="39" t="s">
         <v>6</v>
       </c>
-      <c r="D9" s="16" t="s">
+      <c r="F10" s="39" t="s">
         <v>6</v>
       </c>
-      <c r="E9" s="16" t="s">
+      <c r="G10" s="39" t="s">
         <v>6</v>
       </c>
-      <c r="F9" s="16" t="s">
+      <c r="H10" s="39" t="s">
         <v>6</v>
       </c>
-      <c r="G9" s="16" t="s">
+      <c r="I10" s="39" t="s">
         <v>6</v>
       </c>
-      <c r="H9" s="16" t="s">
+      <c r="J10" s="39" t="s">
         <v>6</v>
       </c>
-      <c r="I9" s="16" t="s">
+      <c r="K10" s="40" t="s">
         <v>6</v>
       </c>
-      <c r="J9" s="16" t="s">
+      <c r="M10" s="21" t="s">
+        <v>56</v>
+      </c>
+      <c r="N10" s="20"/>
+      <c r="O10" s="20"/>
+      <c r="P10" s="20"/>
+      <c r="Q10" s="20"/>
+      <c r="R10" s="20"/>
+      <c r="S10" s="20"/>
+      <c r="T10" s="20"/>
+      <c r="U10" s="20"/>
+      <c r="V10" s="20"/>
+    </row>
+    <row r="11" spans="2:22" ht="32" customHeight="1">
+      <c r="B11" s="44" t="s">
+        <v>65</v>
+      </c>
+      <c r="C11" s="45"/>
+      <c r="D11" s="45"/>
+      <c r="E11" s="45"/>
+      <c r="F11" s="45"/>
+      <c r="G11" s="45"/>
+      <c r="H11" s="45"/>
+      <c r="I11" s="45"/>
+      <c r="J11" s="45"/>
+      <c r="K11" s="46"/>
+      <c r="M11" s="20"/>
+      <c r="N11" s="20"/>
+      <c r="O11" s="20"/>
+      <c r="P11" s="20"/>
+      <c r="Q11" s="20"/>
+      <c r="R11" s="20"/>
+      <c r="S11" s="20"/>
+      <c r="T11" s="20"/>
+      <c r="U11" s="20"/>
+      <c r="V11" s="20"/>
+    </row>
+    <row r="12" spans="2:22" ht="30" customHeight="1">
+      <c r="B12" s="44"/>
+      <c r="C12" s="45"/>
+      <c r="D12" s="45"/>
+      <c r="E12" s="45"/>
+      <c r="F12" s="45"/>
+      <c r="G12" s="45"/>
+      <c r="H12" s="45"/>
+      <c r="I12" s="45"/>
+      <c r="J12" s="45"/>
+      <c r="K12" s="46"/>
+      <c r="M12" s="20"/>
+      <c r="N12" s="20"/>
+      <c r="O12" s="20"/>
+      <c r="P12" s="20"/>
+      <c r="Q12" s="20"/>
+      <c r="R12" s="20"/>
+      <c r="S12" s="20"/>
+      <c r="T12" s="20"/>
+      <c r="U12" s="20"/>
+      <c r="V12" s="20"/>
+    </row>
+    <row r="13" spans="2:22" ht="33" customHeight="1">
+      <c r="B13" s="29" t="s">
+        <v>67</v>
+      </c>
+      <c r="C13" s="36" t="s">
+        <v>45</v>
+      </c>
+      <c r="D13" s="36" t="s">
+        <v>45</v>
+      </c>
+      <c r="E13" s="36" t="s">
+        <v>45</v>
+      </c>
+      <c r="F13" s="36" t="s">
+        <v>45</v>
+      </c>
+      <c r="G13" s="36" t="s">
+        <v>45</v>
+      </c>
+      <c r="H13" s="36" t="s">
+        <v>45</v>
+      </c>
+      <c r="I13" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="J13" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="K13" s="12">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14" spans="2:22" ht="33" customHeight="1">
+      <c r="B14" s="30"/>
+      <c r="C14" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="D14" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="E14" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="F14" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="G14" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="H14" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="I14" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="J14" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="K14" s="32" t="s">
+        <v>46</v>
+      </c>
+      <c r="M14" s="22" t="s">
+        <v>32</v>
+      </c>
+      <c r="N14" s="22"/>
+      <c r="O14" s="22"/>
+      <c r="P14" s="22"/>
+      <c r="Q14" s="22"/>
+      <c r="R14" s="22"/>
+      <c r="S14" s="22"/>
+      <c r="T14" s="22"/>
+      <c r="U14" s="22"/>
+      <c r="V14" s="22"/>
+    </row>
+    <row r="15" spans="2:22" ht="28" customHeight="1">
+      <c r="B15" s="41" t="s">
+        <v>11</v>
+      </c>
+      <c r="C15" s="42" t="s">
+        <v>11</v>
+      </c>
+      <c r="D15" s="42" t="s">
+        <v>11</v>
+      </c>
+      <c r="E15" s="42" t="s">
+        <v>11</v>
+      </c>
+      <c r="F15" s="42" t="s">
+        <v>11</v>
+      </c>
+      <c r="G15" s="42" t="s">
+        <v>11</v>
+      </c>
+      <c r="H15" s="42" t="s">
+        <v>11</v>
+      </c>
+      <c r="I15" s="42" t="s">
+        <v>11</v>
+      </c>
+      <c r="J15" s="42" t="s">
+        <v>11</v>
+      </c>
+      <c r="K15" s="43" t="s">
+        <v>11</v>
+      </c>
+      <c r="M15" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="N15" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="O15" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="P15" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q15" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="R15" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="S15" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="T15" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="U15" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="V15" s="15" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="16" spans="2:22" ht="32" customHeight="1">
+      <c r="B16" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G16" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="H16" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="I16" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="J16" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="K16" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="M16" s="23" t="s">
+        <v>34</v>
+      </c>
+      <c r="N16" s="23"/>
+      <c r="O16" s="23"/>
+      <c r="P16" s="23"/>
+      <c r="Q16" s="23"/>
+      <c r="R16" s="23"/>
+      <c r="S16" s="23"/>
+      <c r="T16" s="23"/>
+      <c r="U16" s="23"/>
+      <c r="V16" s="23"/>
+    </row>
+    <row r="17" spans="2:22" ht="26" customHeight="1">
+      <c r="B17" s="14">
+        <v>1</v>
+      </c>
+      <c r="C17" s="6">
+        <v>140</v>
+      </c>
+      <c r="D17" s="6">
+        <v>100</v>
+      </c>
+      <c r="E17" s="6">
+        <v>150</v>
+      </c>
+      <c r="F17" s="6">
+        <v>160</v>
+      </c>
+      <c r="G17" s="6">
+        <v>240</v>
+      </c>
+      <c r="H17" s="6">
+        <v>310</v>
+      </c>
+      <c r="I17" s="6">
+        <v>250</v>
+      </c>
+      <c r="J17" s="47"/>
+      <c r="K17" s="48"/>
+      <c r="M17" s="23"/>
+      <c r="N17" s="23"/>
+      <c r="O17" s="23"/>
+      <c r="P17" s="23"/>
+      <c r="Q17" s="23"/>
+      <c r="R17" s="23"/>
+      <c r="S17" s="23"/>
+      <c r="T17" s="23"/>
+      <c r="U17" s="23"/>
+      <c r="V17" s="23"/>
+    </row>
+    <row r="18" spans="2:22" ht="26" customHeight="1">
+      <c r="B18" s="14">
+        <v>2</v>
+      </c>
+      <c r="C18" s="7">
+        <v>130</v>
+      </c>
+      <c r="D18" s="7">
+        <v>95</v>
+      </c>
+      <c r="E18" s="7">
+        <v>140</v>
+      </c>
+      <c r="F18" s="7">
+        <v>150</v>
+      </c>
+      <c r="G18" s="7">
+        <v>230</v>
+      </c>
+      <c r="H18" s="7">
+        <v>300</v>
+      </c>
+      <c r="I18" s="7">
+        <v>240</v>
+      </c>
+      <c r="J18" s="47"/>
+      <c r="K18" s="48"/>
+      <c r="M18" s="23"/>
+      <c r="N18" s="23"/>
+      <c r="O18" s="23"/>
+      <c r="P18" s="23"/>
+      <c r="Q18" s="23"/>
+      <c r="R18" s="23"/>
+      <c r="S18" s="23"/>
+      <c r="T18" s="23"/>
+      <c r="U18" s="23"/>
+      <c r="V18" s="23"/>
+    </row>
+    <row r="19" spans="2:22" ht="26" customHeight="1">
+      <c r="B19" s="14">
+        <v>3</v>
+      </c>
+      <c r="C19" s="6">
+        <v>120</v>
+      </c>
+      <c r="D19" s="6">
+        <v>90</v>
+      </c>
+      <c r="E19" s="6">
+        <v>130</v>
+      </c>
+      <c r="F19" s="6">
+        <v>140</v>
+      </c>
+      <c r="G19" s="6">
+        <v>220</v>
+      </c>
+      <c r="H19" s="6">
+        <v>295</v>
+      </c>
+      <c r="I19" s="6">
+        <v>225</v>
+      </c>
+      <c r="J19" s="47"/>
+      <c r="K19" s="48"/>
+    </row>
+    <row r="20" spans="2:22" ht="26" customHeight="1">
+      <c r="B20" s="14">
+        <v>4</v>
+      </c>
+      <c r="C20" s="7">
+        <v>125</v>
+      </c>
+      <c r="D20" s="7">
+        <v>90</v>
+      </c>
+      <c r="E20" s="7">
+        <v>135</v>
+      </c>
+      <c r="F20" s="7">
+        <v>145</v>
+      </c>
+      <c r="G20" s="7">
+        <v>230</v>
+      </c>
+      <c r="H20" s="7">
+        <v>305</v>
+      </c>
+      <c r="I20" s="7">
+        <v>230</v>
+      </c>
+      <c r="J20" s="47"/>
+      <c r="K20" s="48"/>
+      <c r="M20" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="N20" s="22"/>
+      <c r="O20" s="22"/>
+      <c r="P20" s="22"/>
+      <c r="Q20" s="22"/>
+      <c r="R20" s="22"/>
+      <c r="S20" s="22"/>
+      <c r="T20" s="22"/>
+      <c r="U20" s="22"/>
+      <c r="V20" s="22"/>
+    </row>
+    <row r="21" spans="2:22" ht="26" customHeight="1">
+      <c r="B21" s="14">
+        <v>5</v>
+      </c>
+      <c r="C21" s="6">
+        <v>110</v>
+      </c>
+      <c r="D21" s="6">
+        <v>85</v>
+      </c>
+      <c r="E21" s="6">
+        <v>120</v>
+      </c>
+      <c r="F21" s="6">
+        <v>130</v>
+      </c>
+      <c r="G21" s="6">
+        <v>215</v>
+      </c>
+      <c r="H21" s="6">
+        <v>290</v>
+      </c>
+      <c r="I21" s="6">
+        <v>215</v>
+      </c>
+      <c r="J21" s="47"/>
+      <c r="K21" s="48"/>
+      <c r="M21" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="N21" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="O21" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="P21" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q21" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="R21" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="S21" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="T21" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="U21" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="V21" s="15" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="22" spans="2:22" ht="26" customHeight="1">
+      <c r="B22" s="14">
         <v>6</v>
       </c>
-    </row>
-    <row r="10" spans="1:10" ht="32" customHeight="1">
-      <c r="A10" s="16" t="s">
-        <v>45</v>
-      </c>
-      <c r="B10" s="16" t="s">
-        <v>45</v>
-      </c>
-      <c r="C10" s="16" t="s">
-        <v>45</v>
-      </c>
-      <c r="D10" s="16" t="s">
-        <v>45</v>
-      </c>
-      <c r="E10" s="16" t="s">
-        <v>45</v>
-      </c>
-      <c r="F10" s="16" t="s">
-        <v>45</v>
-      </c>
-      <c r="G10" s="16" t="s">
-        <v>45</v>
-      </c>
-      <c r="H10" s="16" t="s">
-        <v>45</v>
-      </c>
-      <c r="I10" s="16" t="s">
-        <v>45</v>
-      </c>
-      <c r="J10" s="16" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" ht="30" customHeight="1">
-      <c r="A11" s="16" t="s">
+      <c r="C22" s="7">
+        <v>100</v>
+      </c>
+      <c r="D22" s="7">
+        <v>80</v>
+      </c>
+      <c r="E22" s="7">
+        <v>110</v>
+      </c>
+      <c r="F22" s="7">
+        <v>120</v>
+      </c>
+      <c r="G22" s="7">
+        <v>205</v>
+      </c>
+      <c r="H22" s="7">
+        <v>280</v>
+      </c>
+      <c r="I22" s="7">
+        <v>200</v>
+      </c>
+      <c r="J22" s="47"/>
+      <c r="K22" s="48"/>
+      <c r="M22" s="23" t="s">
+        <v>34</v>
+      </c>
+      <c r="N22" s="23"/>
+      <c r="O22" s="23"/>
+      <c r="P22" s="23"/>
+      <c r="Q22" s="23"/>
+      <c r="R22" s="23"/>
+      <c r="S22" s="23"/>
+      <c r="T22" s="23"/>
+      <c r="U22" s="23"/>
+      <c r="V22" s="23"/>
+    </row>
+    <row r="23" spans="2:22" ht="26" customHeight="1">
+      <c r="B23" s="14">
+        <v>7</v>
+      </c>
+      <c r="C23" s="6">
+        <v>90</v>
+      </c>
+      <c r="D23" s="6">
+        <v>80</v>
+      </c>
+      <c r="E23" s="6">
+        <v>100</v>
+      </c>
+      <c r="F23" s="6">
+        <v>110</v>
+      </c>
+      <c r="G23" s="6">
+        <v>195</v>
+      </c>
+      <c r="H23" s="6">
+        <v>275</v>
+      </c>
+      <c r="I23" s="6">
+        <v>185</v>
+      </c>
+      <c r="J23" s="47"/>
+      <c r="K23" s="48"/>
+      <c r="M23" s="23"/>
+      <c r="N23" s="23"/>
+      <c r="O23" s="23"/>
+      <c r="P23" s="23"/>
+      <c r="Q23" s="23"/>
+      <c r="R23" s="23"/>
+      <c r="S23" s="23"/>
+      <c r="T23" s="23"/>
+      <c r="U23" s="23"/>
+      <c r="V23" s="23"/>
+    </row>
+    <row r="24" spans="2:22" ht="26" customHeight="1">
+      <c r="B24" s="14">
         <v>8</v>
       </c>
-      <c r="B11" s="16" t="s">
-        <v>8</v>
-      </c>
-      <c r="C11" s="16" t="s">
-        <v>8</v>
-      </c>
-      <c r="D11" s="16" t="s">
-        <v>8</v>
-      </c>
-      <c r="E11" s="16" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" s="16" t="s">
-        <v>8</v>
-      </c>
-      <c r="G11" s="16" t="s">
-        <v>8</v>
-      </c>
-      <c r="H11" s="16" t="s">
-        <v>8</v>
-      </c>
-      <c r="I11" s="16" t="s">
-        <v>8</v>
-      </c>
-      <c r="J11" s="16" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" ht="23" customHeight="1">
-      <c r="A12" s="16" t="s">
-        <v>46</v>
-      </c>
-      <c r="B12" s="16" t="s">
-        <v>46</v>
-      </c>
-      <c r="C12" s="16" t="s">
-        <v>46</v>
-      </c>
-      <c r="D12" s="16" t="s">
-        <v>46</v>
-      </c>
-      <c r="E12" s="16" t="s">
-        <v>46</v>
-      </c>
-      <c r="F12" s="16" t="s">
-        <v>46</v>
-      </c>
-      <c r="G12" s="16" t="s">
-        <v>46</v>
-      </c>
-      <c r="H12" s="16" t="s">
-        <v>46</v>
-      </c>
-      <c r="I12" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="J12" s="3">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" ht="33" customHeight="1">
-      <c r="A13" s="16" t="s">
-        <v>47</v>
-      </c>
-      <c r="B13" s="16" t="s">
-        <v>47</v>
-      </c>
-      <c r="C13" s="16" t="s">
-        <v>47</v>
-      </c>
-      <c r="D13" s="16" t="s">
-        <v>47</v>
-      </c>
-      <c r="E13" s="16" t="s">
-        <v>47</v>
-      </c>
-      <c r="F13" s="16" t="s">
-        <v>47</v>
-      </c>
-      <c r="G13" s="16" t="s">
-        <v>47</v>
-      </c>
-      <c r="H13" s="16" t="s">
-        <v>47</v>
-      </c>
-      <c r="I13" s="16" t="s">
-        <v>47</v>
-      </c>
-      <c r="J13" s="16" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" ht="28" customHeight="1">
-      <c r="A14" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="B14" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="C14" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="D14" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E14" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="F14" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="G14" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="H14" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="I14" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="J14" s="15" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" ht="32" customHeight="1">
-      <c r="A15" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="E15" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="F15" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="G15" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="H15" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="I15" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="J15" s="5" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" ht="26" customHeight="1">
-      <c r="A16" s="6">
-        <v>1</v>
-      </c>
-      <c r="B16" s="6">
-        <v>140</v>
-      </c>
-      <c r="C16" s="6">
+      <c r="C24" s="7">
+        <v>80</v>
+      </c>
+      <c r="D24" s="7">
+        <v>80</v>
+      </c>
+      <c r="E24" s="7">
+        <v>90</v>
+      </c>
+      <c r="F24" s="7">
         <v>100</v>
       </c>
-      <c r="D16" s="6">
-        <v>150</v>
-      </c>
-      <c r="E16" s="6">
-        <v>160</v>
-      </c>
-      <c r="F16" s="6">
-        <v>240</v>
-      </c>
-      <c r="G16" s="6">
-        <v>310</v>
-      </c>
-      <c r="H16" s="6">
-        <v>250</v>
-      </c>
-      <c r="I16" s="8"/>
-      <c r="J16" s="9"/>
-    </row>
-    <row r="17" spans="1:10" ht="26" customHeight="1">
-      <c r="A17" s="7">
-        <v>2</v>
-      </c>
-      <c r="B17" s="7">
-        <v>130</v>
-      </c>
-      <c r="C17" s="7">
-        <v>95</v>
-      </c>
-      <c r="D17" s="7">
-        <v>140</v>
-      </c>
-      <c r="E17" s="7">
-        <v>150</v>
-      </c>
-      <c r="F17" s="7">
-        <v>230</v>
-      </c>
-      <c r="G17" s="7">
-        <v>300</v>
-      </c>
-      <c r="H17" s="7">
-        <v>240</v>
-      </c>
-      <c r="I17" s="8"/>
-      <c r="J17" s="9"/>
-    </row>
-    <row r="18" spans="1:10" ht="26" customHeight="1">
-      <c r="A18" s="6">
-        <v>3</v>
-      </c>
-      <c r="B18" s="6">
-        <v>120</v>
-      </c>
-      <c r="C18" s="6">
-        <v>90</v>
-      </c>
-      <c r="D18" s="6">
-        <v>130</v>
-      </c>
-      <c r="E18" s="6">
-        <v>140</v>
-      </c>
-      <c r="F18" s="6">
-        <v>220</v>
-      </c>
-      <c r="G18" s="6">
-        <v>295</v>
-      </c>
-      <c r="H18" s="6">
-        <v>225</v>
-      </c>
-      <c r="I18" s="8"/>
-      <c r="J18" s="9"/>
-    </row>
-    <row r="19" spans="1:10" ht="26" customHeight="1">
-      <c r="A19" s="7">
-        <v>4</v>
-      </c>
-      <c r="B19" s="7">
-        <v>125</v>
-      </c>
-      <c r="C19" s="7">
-        <v>90</v>
-      </c>
-      <c r="D19" s="7">
-        <v>135</v>
-      </c>
-      <c r="E19" s="7">
-        <v>145</v>
-      </c>
-      <c r="F19" s="7">
-        <v>230</v>
-      </c>
-      <c r="G19" s="7">
-        <v>305</v>
-      </c>
-      <c r="H19" s="7">
-        <v>230</v>
-      </c>
-      <c r="I19" s="8"/>
-      <c r="J19" s="9"/>
-    </row>
-    <row r="20" spans="1:10" ht="26" customHeight="1">
-      <c r="A20" s="6">
-        <v>5</v>
-      </c>
-      <c r="B20" s="6">
-        <v>110</v>
-      </c>
-      <c r="C20" s="6">
-        <v>85</v>
-      </c>
-      <c r="D20" s="6">
-        <v>120</v>
-      </c>
-      <c r="E20" s="6">
-        <v>130</v>
-      </c>
-      <c r="F20" s="6">
-        <v>215</v>
-      </c>
-      <c r="G20" s="6">
-        <v>290</v>
-      </c>
-      <c r="H20" s="6">
-        <v>215</v>
-      </c>
-      <c r="I20" s="8"/>
-      <c r="J20" s="9"/>
-    </row>
-    <row r="21" spans="1:10" ht="26" customHeight="1">
-      <c r="A21" s="7">
-        <v>6</v>
-      </c>
-      <c r="B21" s="7">
-        <v>100</v>
-      </c>
-      <c r="C21" s="7">
-        <v>80</v>
-      </c>
-      <c r="D21" s="7">
-        <v>110</v>
-      </c>
-      <c r="E21" s="7">
-        <v>120</v>
-      </c>
-      <c r="F21" s="7">
-        <v>205</v>
-      </c>
-      <c r="G21" s="7">
-        <v>280</v>
-      </c>
-      <c r="H21" s="7">
-        <v>200</v>
-      </c>
-      <c r="I21" s="8"/>
-      <c r="J21" s="9"/>
-    </row>
-    <row r="22" spans="1:10" ht="26" customHeight="1">
-      <c r="A22" s="6">
-        <v>7</v>
-      </c>
-      <c r="B22" s="6">
-        <v>90</v>
-      </c>
-      <c r="C22" s="6">
-        <v>80</v>
-      </c>
-      <c r="D22" s="6">
-        <v>100</v>
-      </c>
-      <c r="E22" s="6">
-        <v>110</v>
-      </c>
-      <c r="F22" s="6">
-        <v>195</v>
-      </c>
-      <c r="G22" s="6">
-        <v>275</v>
-      </c>
-      <c r="H22" s="6">
+      <c r="G24" s="7">
         <v>185</v>
       </c>
-      <c r="I22" s="8"/>
-      <c r="J22" s="9"/>
-    </row>
-    <row r="23" spans="1:10" ht="26" customHeight="1">
-      <c r="A23" s="7">
-        <v>8</v>
-      </c>
-      <c r="B23" s="7">
-        <v>80</v>
-      </c>
-      <c r="C23" s="7">
-        <v>80</v>
-      </c>
-      <c r="D23" s="7">
-        <v>90</v>
-      </c>
-      <c r="E23" s="7">
-        <v>100</v>
-      </c>
-      <c r="F23" s="7">
-        <v>185</v>
-      </c>
-      <c r="G23" s="7">
+      <c r="H24" s="7">
         <v>265</v>
       </c>
-      <c r="H23" s="7">
+      <c r="I24" s="7">
         <v>170</v>
       </c>
-      <c r="I23" s="8"/>
-      <c r="J23" s="9"/>
-    </row>
-    <row r="24" spans="1:10" ht="23" customHeight="1">
-      <c r="A24" s="1"/>
-      <c r="B24" s="1"/>
-      <c r="C24" s="1"/>
-      <c r="D24" s="1"/>
-      <c r="E24" s="1"/>
-      <c r="F24" s="1"/>
-      <c r="G24" s="1"/>
-      <c r="H24" s="1"/>
-      <c r="I24" s="1"/>
-      <c r="J24" s="1"/>
-    </row>
-    <row r="25" spans="1:10" ht="23" customHeight="1">
-      <c r="A25" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="B25" s="11"/>
-      <c r="C25" s="11"/>
-      <c r="D25" s="11"/>
-      <c r="E25" s="11"/>
-      <c r="F25" s="11"/>
-      <c r="G25" s="11"/>
-      <c r="H25" s="11"/>
+      <c r="J24" s="47"/>
+      <c r="K24" s="48"/>
+      <c r="M24" s="23"/>
+      <c r="N24" s="23"/>
+      <c r="O24" s="23"/>
+      <c r="P24" s="23"/>
+      <c r="Q24" s="23"/>
+      <c r="R24" s="23"/>
+      <c r="S24" s="23"/>
+      <c r="T24" s="23"/>
+      <c r="U24" s="23"/>
+      <c r="V24" s="23"/>
+    </row>
+    <row r="25" spans="2:22" ht="23" customHeight="1">
+      <c r="B25" s="1"/>
+      <c r="C25" s="1"/>
+      <c r="D25" s="1"/>
+      <c r="E25" s="1"/>
+      <c r="F25" s="1"/>
+      <c r="G25" s="1"/>
+      <c r="H25" s="1"/>
       <c r="I25" s="1"/>
       <c r="J25" s="1"/>
-    </row>
-    <row r="26" spans="1:10" ht="23" customHeight="1">
-      <c r="A26" s="1"/>
-      <c r="B26" s="1"/>
-      <c r="C26" s="1"/>
-      <c r="D26" s="1"/>
-      <c r="E26" s="1"/>
-      <c r="F26" s="1"/>
-      <c r="G26" s="1"/>
-      <c r="H26" s="1"/>
-      <c r="I26" s="1"/>
+      <c r="K25" s="1"/>
+      <c r="M25" s="1"/>
+      <c r="N25" s="1"/>
+      <c r="O25" s="1"/>
+      <c r="P25" s="1"/>
+      <c r="Q25" s="1"/>
+      <c r="R25" s="1"/>
+      <c r="S25" s="1"/>
+      <c r="T25" s="1"/>
+      <c r="U25" s="1"/>
+      <c r="V25" s="1"/>
+    </row>
+    <row r="26" spans="2:22" ht="23" customHeight="1">
+      <c r="B26" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C26" s="49"/>
+      <c r="D26" s="49"/>
+      <c r="E26" s="49"/>
+      <c r="F26" s="49"/>
+      <c r="G26" s="49"/>
+      <c r="H26" s="49"/>
+      <c r="I26" s="49"/>
       <c r="J26" s="1"/>
-    </row>
-    <row r="27" spans="1:10" ht="28" customHeight="1">
-      <c r="A27" s="15" t="s">
+      <c r="K26" s="1"/>
+      <c r="M26" s="22" t="s">
+        <v>37</v>
+      </c>
+      <c r="N26" s="22"/>
+      <c r="O26" s="22"/>
+      <c r="P26" s="22"/>
+      <c r="Q26" s="22"/>
+      <c r="R26" s="22"/>
+      <c r="S26" s="22"/>
+      <c r="T26" s="22"/>
+      <c r="U26" s="22"/>
+      <c r="V26" s="22"/>
+    </row>
+    <row r="27" spans="2:22" ht="23" customHeight="1">
+      <c r="B27" s="1"/>
+      <c r="C27" s="1"/>
+      <c r="D27" s="1"/>
+      <c r="E27" s="1"/>
+      <c r="F27" s="1"/>
+      <c r="G27" s="1"/>
+      <c r="H27" s="1"/>
+      <c r="I27" s="1"/>
+      <c r="J27" s="1"/>
+      <c r="K27" s="1"/>
+      <c r="M27" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="N27" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="O27" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="P27" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q27" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="R27" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="S27" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="T27" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="U27" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="V27" s="15" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="28" spans="2:22" ht="28" customHeight="1">
+      <c r="B28" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="B27" s="15" t="s">
+      <c r="C28" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="C27" s="15" t="s">
+      <c r="D28" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="D27" s="15" t="s">
+      <c r="E28" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="E27" s="15" t="s">
+      <c r="F28" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="F27" s="15" t="s">
+      <c r="G28" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="G27" s="15" t="s">
+      <c r="H28" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="H27" s="15" t="s">
+      <c r="I28" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="I27" s="15" t="s">
+      <c r="J28" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="J27" s="15" t="s">
+      <c r="K28" s="8" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="28" spans="1:10" ht="23" customHeight="1">
-      <c r="A28" s="16" t="s">
+      <c r="M28" s="23" t="s">
+        <v>34</v>
+      </c>
+      <c r="N28" s="23"/>
+      <c r="O28" s="23"/>
+      <c r="P28" s="23"/>
+      <c r="Q28" s="23"/>
+      <c r="R28" s="23"/>
+      <c r="S28" s="23"/>
+      <c r="T28" s="23"/>
+      <c r="U28" s="23"/>
+      <c r="V28" s="23"/>
+    </row>
+    <row r="29" spans="2:22" ht="23" customHeight="1">
+      <c r="B29" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="B28" s="16" t="s">
+      <c r="C29" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="C28" s="16" t="s">
+      <c r="D29" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="D28" s="10"/>
-      <c r="E28" s="1"/>
-      <c r="F28" s="1"/>
-      <c r="G28" s="1"/>
-      <c r="H28" s="1"/>
-      <c r="I28" s="1"/>
-      <c r="J28" s="1"/>
-    </row>
-    <row r="29" spans="1:10" ht="23" customHeight="1">
-      <c r="A29" s="16" t="s">
-        <v>25</v>
-      </c>
-      <c r="B29" s="16" t="s">
-        <v>25</v>
-      </c>
-      <c r="C29" s="16" t="s">
-        <v>25</v>
-      </c>
-      <c r="D29" s="10"/>
-      <c r="E29" s="1"/>
+      <c r="E29" s="50"/>
       <c r="F29" s="1"/>
       <c r="G29" s="1"/>
       <c r="H29" s="1"/>
       <c r="I29" s="1"/>
       <c r="J29" s="1"/>
-    </row>
-    <row r="30" spans="1:10" ht="23" customHeight="1">
-      <c r="A30" s="16" t="s">
-        <v>26</v>
-      </c>
-      <c r="B30" s="16" t="s">
-        <v>26</v>
-      </c>
-      <c r="C30" s="16" t="s">
-        <v>26</v>
-      </c>
-      <c r="D30" s="10"/>
-      <c r="E30" s="1"/>
+      <c r="K29" s="1"/>
+      <c r="M29" s="23"/>
+      <c r="N29" s="23"/>
+      <c r="O29" s="23"/>
+      <c r="P29" s="23"/>
+      <c r="Q29" s="23"/>
+      <c r="R29" s="23"/>
+      <c r="S29" s="23"/>
+      <c r="T29" s="23"/>
+      <c r="U29" s="23"/>
+      <c r="V29" s="23"/>
+    </row>
+    <row r="30" spans="2:22" ht="23" customHeight="1">
+      <c r="B30" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="C30" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="D30" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="E30" s="51"/>
       <c r="F30" s="1"/>
       <c r="G30" s="1"/>
       <c r="H30" s="1"/>
       <c r="I30" s="1"/>
       <c r="J30" s="1"/>
-    </row>
-    <row r="31" spans="1:10" ht="23" customHeight="1">
-      <c r="A31" s="16" t="s">
-        <v>27</v>
-      </c>
-      <c r="B31" s="16" t="s">
-        <v>27</v>
-      </c>
-      <c r="C31" s="16" t="s">
-        <v>27</v>
-      </c>
-      <c r="D31" s="10"/>
-      <c r="E31" s="1"/>
+      <c r="K30" s="1"/>
+      <c r="M30" s="23"/>
+      <c r="N30" s="23"/>
+      <c r="O30" s="23"/>
+      <c r="P30" s="23"/>
+      <c r="Q30" s="23"/>
+      <c r="R30" s="23"/>
+      <c r="S30" s="23"/>
+      <c r="T30" s="23"/>
+      <c r="U30" s="23"/>
+      <c r="V30" s="23"/>
+    </row>
+    <row r="31" spans="2:22" ht="23" customHeight="1">
+      <c r="B31" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="C31" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="D31" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="E31" s="51"/>
       <c r="F31" s="1"/>
       <c r="G31" s="1"/>
       <c r="H31" s="1"/>
       <c r="I31" s="1"/>
       <c r="J31" s="1"/>
-    </row>
-    <row r="32" spans="1:10" ht="23" customHeight="1">
-      <c r="A32" s="16" t="s">
-        <v>28</v>
-      </c>
-      <c r="B32" s="16" t="s">
-        <v>28</v>
-      </c>
-      <c r="C32" s="16" t="s">
-        <v>28</v>
-      </c>
-      <c r="D32" s="10"/>
-      <c r="E32" s="1"/>
+      <c r="K31" s="1"/>
+    </row>
+    <row r="32" spans="2:22" ht="23" customHeight="1">
+      <c r="B32" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="C32" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="D32" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="E32" s="51"/>
       <c r="F32" s="1"/>
       <c r="G32" s="1"/>
       <c r="H32" s="1"/>
       <c r="I32" s="1"/>
       <c r="J32" s="1"/>
-    </row>
-    <row r="33" spans="1:10" ht="23" customHeight="1">
-      <c r="A33" s="1"/>
-      <c r="B33" s="1"/>
-      <c r="C33" s="1"/>
-      <c r="D33" s="1"/>
-      <c r="E33" s="1"/>
+      <c r="K32" s="1"/>
+      <c r="M32" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="N32" s="22"/>
+      <c r="O32" s="22"/>
+      <c r="P32" s="22"/>
+      <c r="Q32" s="22"/>
+      <c r="R32" s="22"/>
+      <c r="S32" s="22"/>
+      <c r="T32" s="22"/>
+      <c r="U32" s="22"/>
+      <c r="V32" s="22"/>
+    </row>
+    <row r="33" spans="2:22" ht="23" customHeight="1">
+      <c r="B33" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="C33" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="D33" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="E33" s="51"/>
       <c r="F33" s="1"/>
       <c r="G33" s="1"/>
       <c r="H33" s="1"/>
       <c r="I33" s="1"/>
       <c r="J33" s="1"/>
-    </row>
-    <row r="34" spans="1:10" ht="23" customHeight="1">
-      <c r="A34" s="17" t="s">
-        <v>48</v>
-      </c>
-      <c r="B34" s="17" t="s">
-        <v>48</v>
-      </c>
-      <c r="C34" s="17" t="s">
-        <v>48</v>
-      </c>
-      <c r="D34" s="17" t="s">
-        <v>48</v>
-      </c>
+      <c r="K33" s="1"/>
+      <c r="M33" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="N33" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="O33" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="P33" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q33" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="R33" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="S33" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="T33" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="U33" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="V33" s="15" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="34" spans="2:22" ht="23" customHeight="1">
+      <c r="B34" s="1"/>
+      <c r="C34" s="1"/>
+      <c r="D34" s="1"/>
       <c r="E34" s="1"/>
       <c r="F34" s="1"/>
       <c r="G34" s="1"/>
       <c r="H34" s="1"/>
       <c r="I34" s="1"/>
       <c r="J34" s="1"/>
-    </row>
-    <row r="35" spans="1:10" ht="23" customHeight="1">
-      <c r="A35" s="17" t="s">
-        <v>48</v>
-      </c>
-      <c r="B35" s="17" t="s">
-        <v>48</v>
-      </c>
-      <c r="C35" s="17" t="s">
-        <v>48</v>
-      </c>
-      <c r="D35" s="17" t="s">
-        <v>48</v>
-      </c>
-      <c r="E35" s="1"/>
+      <c r="K34" s="1"/>
+      <c r="M34" s="23" t="s">
+        <v>34</v>
+      </c>
+      <c r="N34" s="23"/>
+      <c r="O34" s="23"/>
+      <c r="P34" s="23"/>
+      <c r="Q34" s="23"/>
+      <c r="R34" s="23"/>
+      <c r="S34" s="23"/>
+      <c r="T34" s="23"/>
+      <c r="U34" s="23"/>
+      <c r="V34" s="23"/>
+    </row>
+    <row r="35" spans="2:22" ht="23" customHeight="1">
+      <c r="B35" s="21" t="s">
+        <v>68</v>
+      </c>
+      <c r="C35" s="20" t="s">
+        <v>47</v>
+      </c>
+      <c r="D35" s="20" t="s">
+        <v>47</v>
+      </c>
+      <c r="E35" s="20" t="s">
+        <v>47</v>
+      </c>
       <c r="F35" s="1"/>
       <c r="G35" s="1"/>
       <c r="H35" s="1"/>
       <c r="I35" s="1"/>
       <c r="J35" s="1"/>
-    </row>
-    <row r="36" spans="1:10" ht="23" customHeight="1">
-      <c r="A36" s="1"/>
-      <c r="B36" s="1"/>
-      <c r="C36" s="1"/>
-      <c r="D36" s="1"/>
-      <c r="E36" s="1"/>
+      <c r="K35" s="1"/>
+      <c r="M35" s="23"/>
+      <c r="N35" s="23"/>
+      <c r="O35" s="23"/>
+      <c r="P35" s="23"/>
+      <c r="Q35" s="23"/>
+      <c r="R35" s="23"/>
+      <c r="S35" s="23"/>
+      <c r="T35" s="23"/>
+      <c r="U35" s="23"/>
+      <c r="V35" s="23"/>
+    </row>
+    <row r="36" spans="2:22" ht="23" customHeight="1">
+      <c r="B36" s="20" t="s">
+        <v>47</v>
+      </c>
+      <c r="C36" s="20" t="s">
+        <v>47</v>
+      </c>
+      <c r="D36" s="20" t="s">
+        <v>47</v>
+      </c>
+      <c r="E36" s="20" t="s">
+        <v>47</v>
+      </c>
       <c r="F36" s="1"/>
       <c r="G36" s="1"/>
       <c r="H36" s="1"/>
       <c r="I36" s="1"/>
       <c r="J36" s="1"/>
-    </row>
-    <row r="37" spans="1:10" ht="23" customHeight="1">
-      <c r="A37" s="16" t="s">
-        <v>30</v>
-      </c>
-      <c r="B37" s="16" t="s">
-        <v>30</v>
-      </c>
-      <c r="C37" s="16" t="s">
-        <v>30</v>
-      </c>
-      <c r="D37" s="16" t="s">
-        <v>30</v>
-      </c>
+      <c r="K36" s="1"/>
+      <c r="M36" s="23"/>
+      <c r="N36" s="23"/>
+      <c r="O36" s="23"/>
+      <c r="P36" s="23"/>
+      <c r="Q36" s="23"/>
+      <c r="R36" s="23"/>
+      <c r="S36" s="23"/>
+      <c r="T36" s="23"/>
+      <c r="U36" s="23"/>
+      <c r="V36" s="23"/>
+    </row>
+    <row r="37" spans="2:22" ht="23" customHeight="1">
+      <c r="B37" s="1"/>
+      <c r="C37" s="1"/>
+      <c r="D37" s="1"/>
       <c r="E37" s="1"/>
       <c r="F37" s="1"/>
       <c r="G37" s="1"/>
       <c r="H37" s="1"/>
       <c r="I37" s="1"/>
       <c r="J37" s="1"/>
-    </row>
-    <row r="38" spans="1:10" ht="23" customHeight="1">
-      <c r="A38" s="16" t="s">
+      <c r="K37" s="1"/>
+    </row>
+    <row r="38" spans="2:22" ht="23" customHeight="1">
+      <c r="B38" s="21" t="s">
+        <v>69</v>
+      </c>
+      <c r="C38" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="B38" s="16" t="s">
+      <c r="D38" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="C38" s="16" t="s">
+      <c r="E38" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="D38" s="16" t="s">
-        <v>30</v>
-      </c>
-      <c r="E38" s="1"/>
       <c r="F38" s="1"/>
       <c r="G38" s="1"/>
       <c r="H38" s="1"/>
       <c r="I38" s="1"/>
       <c r="J38" s="1"/>
-    </row>
-    <row r="39" spans="1:10" ht="23" customHeight="1">
-      <c r="A39" s="16" t="s">
+      <c r="K38" s="1"/>
+      <c r="M38" s="24" t="s">
+        <v>41</v>
+      </c>
+      <c r="N38" s="24"/>
+      <c r="O38" s="24"/>
+      <c r="P38" s="24"/>
+      <c r="Q38" s="24"/>
+      <c r="R38" s="24"/>
+      <c r="S38" s="24"/>
+      <c r="T38" s="24"/>
+      <c r="U38" s="24"/>
+      <c r="V38" s="24"/>
+    </row>
+    <row r="39" spans="2:22" ht="23" customHeight="1">
+      <c r="B39" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="B39" s="16" t="s">
+      <c r="C39" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="C39" s="16" t="s">
+      <c r="D39" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="D39" s="16" t="s">
+      <c r="E39" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="E39" s="1"/>
       <c r="F39" s="1"/>
       <c r="G39" s="1"/>
       <c r="H39" s="1"/>
       <c r="I39" s="1"/>
       <c r="J39" s="1"/>
-    </row>
-    <row r="40" spans="1:10" ht="23" customHeight="1">
-      <c r="A40" s="1"/>
-      <c r="B40" s="1"/>
-      <c r="C40" s="1"/>
-      <c r="D40" s="1"/>
-      <c r="E40" s="1"/>
+      <c r="K39" s="1"/>
+      <c r="M39" s="25" t="s">
+        <v>42</v>
+      </c>
+      <c r="N39" s="25"/>
+      <c r="O39" s="25"/>
+      <c r="P39" s="25"/>
+      <c r="Q39" s="25"/>
+      <c r="R39" s="25"/>
+      <c r="S39" s="25"/>
+      <c r="T39" s="25"/>
+      <c r="U39" s="25"/>
+      <c r="V39" s="25"/>
+    </row>
+    <row r="40" spans="2:22" ht="23" customHeight="1">
+      <c r="B40" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="C40" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="D40" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="E40" s="20" t="s">
+        <v>30</v>
+      </c>
       <c r="F40" s="1"/>
       <c r="G40" s="1"/>
       <c r="H40" s="1"/>
       <c r="I40" s="1"/>
       <c r="J40" s="1"/>
-    </row>
-    <row r="41" spans="1:10" ht="30" customHeight="1">
-      <c r="A41" s="16" t="s">
-        <v>49</v>
-      </c>
-      <c r="B41" s="16" t="s">
-        <v>49</v>
-      </c>
-      <c r="C41" s="16" t="s">
-        <v>49</v>
-      </c>
-      <c r="D41" s="16" t="s">
-        <v>49</v>
-      </c>
-      <c r="E41" s="16" t="s">
-        <v>49</v>
-      </c>
-      <c r="F41" s="16" t="s">
-        <v>49</v>
-      </c>
-      <c r="G41" s="16" t="s">
-        <v>49</v>
-      </c>
-      <c r="H41" s="16" t="s">
-        <v>49</v>
-      </c>
-      <c r="I41" s="16" t="s">
-        <v>49</v>
-      </c>
-      <c r="J41" s="16" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="42" spans="1:10" ht="23" customHeight="1">
-      <c r="A42" s="1"/>
-      <c r="B42" s="1"/>
-      <c r="C42" s="1"/>
-      <c r="D42" s="1"/>
-      <c r="E42" s="1"/>
-      <c r="F42" s="1"/>
-      <c r="G42" s="1"/>
-      <c r="H42" s="1"/>
-      <c r="I42" s="1"/>
-      <c r="J42" s="1"/>
-    </row>
-    <row r="43" spans="1:10" ht="28" customHeight="1">
-      <c r="A43" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="B43" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="C43" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="D43" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="E43" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="F43" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="G43" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="H43" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="I43" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="J43" s="15" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="44" spans="1:10" ht="34" customHeight="1">
-      <c r="A44" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="B44" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="C44" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="D44" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="E44" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="F44" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="G44" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="H44" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="I44" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="J44" s="16" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="45" spans="1:10" ht="23" customHeight="1">
-      <c r="A45" s="1"/>
-      <c r="B45" s="1"/>
-      <c r="C45" s="1"/>
-      <c r="D45" s="1"/>
-      <c r="E45" s="1"/>
-      <c r="F45" s="1"/>
-      <c r="G45" s="1"/>
-      <c r="H45" s="1"/>
-      <c r="I45" s="1"/>
-      <c r="J45" s="1"/>
-    </row>
-    <row r="46" spans="1:10" ht="23" customHeight="1">
-      <c r="A46" s="18" t="s">
-        <v>32</v>
-      </c>
-      <c r="B46" s="18" t="s">
-        <v>32</v>
-      </c>
-      <c r="C46" s="18" t="s">
-        <v>32</v>
-      </c>
-      <c r="D46" s="18" t="s">
-        <v>32</v>
-      </c>
-      <c r="E46" s="18" t="s">
-        <v>32</v>
-      </c>
-      <c r="F46" s="18" t="s">
-        <v>32</v>
-      </c>
-      <c r="G46" s="18" t="s">
-        <v>32</v>
-      </c>
-      <c r="H46" s="18" t="s">
-        <v>32</v>
-      </c>
-      <c r="I46" s="18" t="s">
-        <v>32</v>
-      </c>
-      <c r="J46" s="18" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="47" spans="1:10" ht="35" customHeight="1">
-      <c r="A47" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="B47" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="C47" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="D47" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="E47" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="F47" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="G47" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="H47" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="I47" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="J47" s="16" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="48" spans="1:10" ht="65" customHeight="1">
-      <c r="A48" s="19" t="s">
+      <c r="K40" s="1"/>
+    </row>
+    <row r="41" spans="2:22" ht="23" customHeight="1">
+      <c r="B41" s="1"/>
+      <c r="C41" s="1"/>
+      <c r="D41" s="1"/>
+      <c r="E41" s="1"/>
+      <c r="F41" s="1"/>
+      <c r="G41" s="1"/>
+      <c r="H41" s="1"/>
+      <c r="I41" s="1"/>
+      <c r="J41" s="1"/>
+      <c r="K41" s="1"/>
+    </row>
+    <row r="42" spans="2:22" ht="30" customHeight="1">
+      <c r="B42" s="52" t="s">
+        <v>70</v>
+      </c>
+      <c r="C42" s="52" t="s">
+        <v>48</v>
+      </c>
+      <c r="D42" s="52" t="s">
+        <v>48</v>
+      </c>
+      <c r="E42" s="52" t="s">
+        <v>48</v>
+      </c>
+      <c r="F42" s="52" t="s">
+        <v>48</v>
+      </c>
+      <c r="G42" s="52" t="s">
+        <v>48</v>
+      </c>
+      <c r="H42" s="52" t="s">
+        <v>48</v>
+      </c>
+      <c r="I42" s="52" t="s">
+        <v>48</v>
+      </c>
+      <c r="J42" s="52" t="s">
+        <v>48</v>
+      </c>
+      <c r="K42" s="52" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="43" spans="2:22" ht="23" customHeight="1">
+      <c r="B43" s="1"/>
+      <c r="C43" s="1"/>
+      <c r="D43" s="1"/>
+      <c r="E43" s="1"/>
+      <c r="F43" s="1"/>
+      <c r="G43" s="1"/>
+      <c r="H43" s="1"/>
+      <c r="I43" s="1"/>
+      <c r="J43" s="1"/>
+      <c r="K43" s="1"/>
+    </row>
+    <row r="44" spans="2:22" ht="23" customHeight="1">
+      <c r="B44" s="1"/>
+      <c r="C44" s="1"/>
+      <c r="D44" s="1"/>
+      <c r="E44" s="1"/>
+      <c r="F44" s="1"/>
+      <c r="G44" s="1"/>
+      <c r="H44" s="1"/>
+      <c r="I44" s="1"/>
+      <c r="J44" s="1"/>
+      <c r="K44" s="1"/>
+    </row>
+    <row r="45" spans="2:22" ht="28" customHeight="1">
+      <c r="B45" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="C45" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="D45" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="E45" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="F45" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="G45" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="H45" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="I45" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="J45" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="K45" s="8" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="46" spans="2:22" ht="23" customHeight="1">
+      <c r="B46" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="C46" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="D46" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="E46" s="53"/>
+      <c r="F46" s="15"/>
+      <c r="G46" s="15"/>
+      <c r="H46" s="15"/>
+      <c r="I46" s="15"/>
+      <c r="J46" s="15"/>
+      <c r="K46" s="15"/>
+    </row>
+    <row r="47" spans="2:22" ht="23" customHeight="1">
+      <c r="B47" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="C47" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="D47" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="E47" s="54"/>
+      <c r="F47" s="15"/>
+      <c r="G47" s="15"/>
+      <c r="H47" s="15"/>
+      <c r="I47" s="15"/>
+      <c r="J47" s="15"/>
+      <c r="K47" s="15"/>
+    </row>
+    <row r="48" spans="2:22" ht="23" customHeight="1">
+      <c r="B48" s="1"/>
+      <c r="C48" s="1"/>
+      <c r="D48" s="1"/>
+      <c r="E48" s="1"/>
+      <c r="F48" s="1"/>
+      <c r="G48" s="1"/>
+      <c r="H48" s="1"/>
+      <c r="I48" s="1"/>
+      <c r="J48" s="1"/>
+      <c r="K48" s="1"/>
+    </row>
+    <row r="49" spans="2:11" ht="30" customHeight="1">
+      <c r="B49" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="C49" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="D49" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="E49" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="F49" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="G49" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="H49" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="I49" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="J49" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="K49" s="15" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="50" spans="2:11" ht="120" customHeight="1">
+      <c r="B50" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="B48" s="19" t="s">
+      <c r="C50" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="C48" s="19" t="s">
+      <c r="D50" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="D48" s="19" t="s">
+      <c r="E50" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="E48" s="19" t="s">
+      <c r="F50" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="F48" s="19" t="s">
+      <c r="G50" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="G48" s="19" t="s">
+      <c r="H50" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="H48" s="19" t="s">
+      <c r="I50" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="I48" s="19" t="s">
+      <c r="J50" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="J48" s="19" t="s">
+      <c r="K50" s="4" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="49" spans="1:10" ht="23" customHeight="1">
-      <c r="A49" s="1"/>
-      <c r="B49" s="1"/>
-      <c r="C49" s="1"/>
-      <c r="D49" s="1"/>
-      <c r="E49" s="1"/>
-      <c r="F49" s="1"/>
-      <c r="G49" s="1"/>
-      <c r="H49" s="1"/>
-      <c r="I49" s="1"/>
-      <c r="J49" s="1"/>
-    </row>
-    <row r="50" spans="1:10" ht="23" customHeight="1">
-      <c r="A50" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="B50" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="C50" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="D50" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="E50" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="F50" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="G50" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="H50" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="I50" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="J50" s="18" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="51" spans="1:10" ht="35" customHeight="1">
-      <c r="A51" s="16" t="s">
-        <v>52</v>
-      </c>
-      <c r="B51" s="16" t="s">
-        <v>52</v>
-      </c>
-      <c r="C51" s="16" t="s">
-        <v>52</v>
-      </c>
-      <c r="D51" s="16" t="s">
-        <v>52</v>
-      </c>
-      <c r="E51" s="16" t="s">
-        <v>52</v>
-      </c>
-      <c r="F51" s="16" t="s">
-        <v>52</v>
-      </c>
-      <c r="G51" s="16" t="s">
-        <v>52</v>
-      </c>
-      <c r="H51" s="16" t="s">
-        <v>52</v>
-      </c>
-      <c r="I51" s="16" t="s">
-        <v>52</v>
-      </c>
-      <c r="J51" s="16" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="52" spans="1:10" ht="65" customHeight="1">
-      <c r="A52" s="19" t="s">
-        <v>34</v>
-      </c>
-      <c r="B52" s="19" t="s">
-        <v>34</v>
-      </c>
-      <c r="C52" s="19" t="s">
-        <v>34</v>
-      </c>
-      <c r="D52" s="19" t="s">
-        <v>34</v>
-      </c>
-      <c r="E52" s="19" t="s">
-        <v>34</v>
-      </c>
-      <c r="F52" s="19" t="s">
-        <v>34</v>
-      </c>
-      <c r="G52" s="19" t="s">
-        <v>34</v>
-      </c>
-      <c r="H52" s="19" t="s">
-        <v>34</v>
-      </c>
-      <c r="I52" s="19" t="s">
-        <v>34</v>
-      </c>
-      <c r="J52" s="19" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="53" spans="1:10" ht="23" customHeight="1">
-      <c r="A53" s="1"/>
+    <row r="51" spans="2:11" ht="23" customHeight="1">
+      <c r="B51" s="1"/>
+      <c r="C51" s="1"/>
+      <c r="D51" s="1"/>
+      <c r="E51" s="1"/>
+      <c r="F51" s="1"/>
+      <c r="G51" s="1"/>
+      <c r="H51" s="1"/>
+      <c r="I51" s="1"/>
+      <c r="J51" s="1"/>
+      <c r="K51" s="1"/>
+    </row>
+    <row r="52" spans="2:11" ht="23" customHeight="1">
+      <c r="B52" s="1"/>
+      <c r="C52" s="1"/>
+      <c r="D52" s="1"/>
+      <c r="E52" s="1"/>
+      <c r="F52" s="1"/>
+      <c r="G52" s="1"/>
+      <c r="H52" s="1"/>
+      <c r="I52" s="1"/>
+      <c r="J52" s="1"/>
+      <c r="K52" s="1"/>
+    </row>
+    <row r="53" spans="2:11" ht="23" customHeight="1">
       <c r="B53" s="1"/>
       <c r="C53" s="1"/>
       <c r="D53" s="1"/>
@@ -4499,585 +5011,90 @@
       <c r="H53" s="1"/>
       <c r="I53" s="1"/>
       <c r="J53" s="1"/>
-    </row>
-    <row r="54" spans="1:10" ht="23" customHeight="1">
-      <c r="A54" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="B54" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="C54" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="D54" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="E54" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="F54" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="G54" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="H54" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="I54" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="J54" s="18" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="55" spans="1:10" ht="35" customHeight="1">
-      <c r="A55" s="16" t="s">
-        <v>53</v>
-      </c>
-      <c r="B55" s="16" t="s">
-        <v>53</v>
-      </c>
-      <c r="C55" s="16" t="s">
-        <v>53</v>
-      </c>
-      <c r="D55" s="16" t="s">
-        <v>53</v>
-      </c>
-      <c r="E55" s="16" t="s">
-        <v>53</v>
-      </c>
-      <c r="F55" s="16" t="s">
-        <v>53</v>
-      </c>
-      <c r="G55" s="16" t="s">
-        <v>53</v>
-      </c>
-      <c r="H55" s="16" t="s">
-        <v>53</v>
-      </c>
-      <c r="I55" s="16" t="s">
-        <v>53</v>
-      </c>
-      <c r="J55" s="16" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="56" spans="1:10" ht="65" customHeight="1">
-      <c r="A56" s="19" t="s">
-        <v>34</v>
-      </c>
-      <c r="B56" s="19" t="s">
-        <v>34</v>
-      </c>
-      <c r="C56" s="19" t="s">
-        <v>34</v>
-      </c>
-      <c r="D56" s="19" t="s">
-        <v>34</v>
-      </c>
-      <c r="E56" s="19" t="s">
-        <v>34</v>
-      </c>
-      <c r="F56" s="19" t="s">
-        <v>34</v>
-      </c>
-      <c r="G56" s="19" t="s">
-        <v>34</v>
-      </c>
-      <c r="H56" s="19" t="s">
-        <v>34</v>
-      </c>
-      <c r="I56" s="19" t="s">
-        <v>34</v>
-      </c>
-      <c r="J56" s="19" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="57" spans="1:10" ht="23" customHeight="1">
-      <c r="A57" s="1"/>
-      <c r="B57" s="1"/>
-      <c r="C57" s="1"/>
-      <c r="D57" s="1"/>
-      <c r="E57" s="1"/>
-      <c r="F57" s="1"/>
-      <c r="G57" s="1"/>
-      <c r="H57" s="1"/>
-      <c r="I57" s="1"/>
-      <c r="J57" s="1"/>
-    </row>
-    <row r="58" spans="1:10" ht="23" customHeight="1">
-      <c r="A58" s="18" t="s">
-        <v>39</v>
-      </c>
-      <c r="B58" s="18" t="s">
-        <v>39</v>
-      </c>
-      <c r="C58" s="18" t="s">
-        <v>39</v>
-      </c>
-      <c r="D58" s="18" t="s">
-        <v>39</v>
-      </c>
-      <c r="E58" s="18" t="s">
-        <v>39</v>
-      </c>
-      <c r="F58" s="18" t="s">
-        <v>39</v>
-      </c>
-      <c r="G58" s="18" t="s">
-        <v>39</v>
-      </c>
-      <c r="H58" s="18" t="s">
-        <v>39</v>
-      </c>
-      <c r="I58" s="18" t="s">
-        <v>39</v>
-      </c>
-      <c r="J58" s="18" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="59" spans="1:10" ht="35" customHeight="1">
-      <c r="A59" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="B59" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="C59" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="D59" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="E59" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="F59" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="G59" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="H59" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="I59" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="J59" s="16" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="60" spans="1:10" ht="65" customHeight="1">
-      <c r="A60" s="19" t="s">
-        <v>34</v>
-      </c>
-      <c r="B60" s="19" t="s">
-        <v>34</v>
-      </c>
-      <c r="C60" s="19" t="s">
-        <v>34</v>
-      </c>
-      <c r="D60" s="19" t="s">
-        <v>34</v>
-      </c>
-      <c r="E60" s="19" t="s">
-        <v>34</v>
-      </c>
-      <c r="F60" s="19" t="s">
-        <v>34</v>
-      </c>
-      <c r="G60" s="19" t="s">
-        <v>34</v>
-      </c>
-      <c r="H60" s="19" t="s">
-        <v>34</v>
-      </c>
-      <c r="I60" s="19" t="s">
-        <v>34</v>
-      </c>
-      <c r="J60" s="19" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="61" spans="1:10" ht="23" customHeight="1">
-      <c r="A61" s="1"/>
-      <c r="B61" s="1"/>
-      <c r="C61" s="1"/>
-      <c r="D61" s="1"/>
-      <c r="E61" s="1"/>
-      <c r="F61" s="1"/>
-      <c r="G61" s="1"/>
-      <c r="H61" s="1"/>
-      <c r="I61" s="1"/>
-      <c r="J61" s="1"/>
-    </row>
-    <row r="62" spans="1:10" ht="30" customHeight="1">
-      <c r="A62" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="B62" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="C62" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="D62" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="E62" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="F62" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="G62" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="H62" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="I62" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="J62" s="13" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="63" spans="1:10" ht="32" customHeight="1">
-      <c r="A63" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="B63" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="C63" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="D63" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="E63" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="F63" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="G63" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="H63" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="I63" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="J63" s="16" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="64" spans="1:10" ht="23" customHeight="1">
-      <c r="A64" s="1"/>
-      <c r="B64" s="1"/>
-      <c r="C64" s="1"/>
-      <c r="D64" s="1"/>
-      <c r="E64" s="1"/>
-      <c r="F64" s="1"/>
-      <c r="G64" s="1"/>
-      <c r="H64" s="1"/>
-      <c r="I64" s="1"/>
-      <c r="J64" s="1"/>
-    </row>
-    <row r="65" spans="1:10" ht="28" customHeight="1">
-      <c r="A65" s="15" t="s">
-        <v>56</v>
-      </c>
-      <c r="B65" s="15" t="s">
-        <v>56</v>
-      </c>
-      <c r="C65" s="15" t="s">
-        <v>56</v>
-      </c>
-      <c r="D65" s="15" t="s">
-        <v>56</v>
-      </c>
-      <c r="E65" s="15" t="s">
-        <v>56</v>
-      </c>
-      <c r="F65" s="15" t="s">
-        <v>56</v>
-      </c>
-      <c r="G65" s="15" t="s">
-        <v>56</v>
-      </c>
-      <c r="H65" s="15" t="s">
-        <v>56</v>
-      </c>
-      <c r="I65" s="15" t="s">
-        <v>56</v>
-      </c>
-      <c r="J65" s="15" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="66" spans="1:10" ht="23" customHeight="1">
-      <c r="A66" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="B66" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="C66" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="D66" s="10"/>
-      <c r="E66" s="16" t="s">
-        <v>58</v>
-      </c>
-      <c r="F66" s="16" t="s">
-        <v>58</v>
-      </c>
-      <c r="G66" s="16" t="s">
-        <v>58</v>
-      </c>
-      <c r="H66" s="16" t="s">
-        <v>58</v>
-      </c>
-      <c r="I66" s="16" t="s">
-        <v>58</v>
-      </c>
-      <c r="J66" s="16" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="67" spans="1:10" ht="23" customHeight="1">
-      <c r="A67" s="16" t="s">
-        <v>59</v>
-      </c>
-      <c r="B67" s="16" t="s">
-        <v>59</v>
-      </c>
-      <c r="C67" s="16" t="s">
-        <v>59</v>
-      </c>
-      <c r="D67" s="11"/>
-      <c r="E67" s="16" t="s">
-        <v>60</v>
-      </c>
-      <c r="F67" s="16" t="s">
-        <v>60</v>
-      </c>
-      <c r="G67" s="16" t="s">
-        <v>60</v>
-      </c>
-      <c r="H67" s="16" t="s">
-        <v>60</v>
-      </c>
-      <c r="I67" s="16" t="s">
-        <v>60</v>
-      </c>
-      <c r="J67" s="16" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="68" spans="1:10" ht="23" customHeight="1">
-      <c r="A68" s="1"/>
-      <c r="B68" s="1"/>
-      <c r="C68" s="1"/>
-      <c r="D68" s="1"/>
-      <c r="E68" s="1"/>
-      <c r="F68" s="1"/>
-      <c r="G68" s="1"/>
-      <c r="H68" s="1"/>
-      <c r="I68" s="1"/>
-      <c r="J68" s="1"/>
-    </row>
-    <row r="69" spans="1:10" ht="30" customHeight="1">
-      <c r="A69" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="B69" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="C69" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="D69" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="E69" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="F69" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="G69" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="H69" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="I69" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="J69" s="16" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="70" spans="1:10" ht="65" customHeight="1">
-      <c r="A70" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="B70" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="C70" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="D70" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="E70" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="F70" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="G70" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="H70" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="I70" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="J70" s="14" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="71" spans="1:10" ht="23" customHeight="1">
-      <c r="A71" s="1"/>
-      <c r="B71" s="1"/>
-      <c r="C71" s="1"/>
-      <c r="D71" s="1"/>
-      <c r="E71" s="1"/>
-      <c r="F71" s="1"/>
-      <c r="G71" s="1"/>
-      <c r="H71" s="1"/>
-      <c r="I71" s="1"/>
-      <c r="J71" s="1"/>
-    </row>
-    <row r="72" spans="1:10" ht="23" customHeight="1">
-      <c r="A72" s="1"/>
-      <c r="B72" s="1"/>
-      <c r="C72" s="1"/>
-      <c r="D72" s="1"/>
-      <c r="E72" s="1"/>
-      <c r="F72" s="1"/>
-      <c r="G72" s="1"/>
-      <c r="H72" s="1"/>
-      <c r="I72" s="1"/>
-      <c r="J72" s="1"/>
-    </row>
-    <row r="73" spans="1:10" ht="23" customHeight="1">
-      <c r="A73" s="1"/>
-      <c r="B73" s="1"/>
-      <c r="C73" s="1"/>
-      <c r="D73" s="1"/>
-      <c r="E73" s="1"/>
-      <c r="F73" s="1"/>
-      <c r="G73" s="1"/>
-      <c r="H73" s="1"/>
-      <c r="I73" s="1"/>
-      <c r="J73" s="1"/>
-    </row>
-    <row r="74" spans="1:10" ht="23" customHeight="1">
-      <c r="A74" s="1"/>
-      <c r="B74" s="1"/>
-      <c r="C74" s="1"/>
-      <c r="D74" s="1"/>
-      <c r="E74" s="1"/>
-      <c r="F74" s="1"/>
-      <c r="G74" s="1"/>
-      <c r="H74" s="1"/>
-      <c r="I74" s="1"/>
-      <c r="J74" s="1"/>
-    </row>
-    <row r="75" spans="1:10" ht="23" customHeight="1">
-      <c r="A75" s="1"/>
-      <c r="B75" s="1"/>
-      <c r="C75" s="1"/>
-      <c r="D75" s="1"/>
-      <c r="E75" s="1"/>
-      <c r="F75" s="1"/>
-      <c r="G75" s="1"/>
-      <c r="H75" s="1"/>
-      <c r="I75" s="1"/>
-      <c r="J75" s="1"/>
-    </row>
-    <row r="76" spans="1:10" ht="23" customHeight="1">
-      <c r="A76" s="1"/>
-      <c r="B76" s="1"/>
-      <c r="C76" s="1"/>
-      <c r="D76" s="1"/>
-      <c r="E76" s="1"/>
-      <c r="F76" s="1"/>
-      <c r="G76" s="1"/>
-      <c r="H76" s="1"/>
-      <c r="I76" s="1"/>
-      <c r="J76" s="1"/>
+      <c r="K53" s="1"/>
+    </row>
+    <row r="54" spans="2:11" ht="23" customHeight="1">
+      <c r="B54" s="1"/>
+      <c r="C54" s="1"/>
+      <c r="D54" s="1"/>
+      <c r="E54" s="1"/>
+      <c r="F54" s="1"/>
+      <c r="G54" s="1"/>
+      <c r="H54" s="1"/>
+      <c r="I54" s="1"/>
+      <c r="J54" s="1"/>
+      <c r="K54" s="1"/>
+    </row>
+    <row r="55" spans="2:11" ht="23" customHeight="1">
+      <c r="B55" s="1"/>
+      <c r="C55" s="1"/>
+      <c r="D55" s="1"/>
+      <c r="E55" s="1"/>
+      <c r="F55" s="1"/>
+      <c r="G55" s="1"/>
+      <c r="H55" s="1"/>
+      <c r="I55" s="1"/>
+      <c r="J55" s="1"/>
+      <c r="K55" s="1"/>
+    </row>
+    <row r="56" spans="2:11" ht="23" customHeight="1">
+      <c r="B56" s="1"/>
+      <c r="C56" s="1"/>
+      <c r="D56" s="1"/>
+      <c r="E56" s="1"/>
+      <c r="F56" s="1"/>
+      <c r="G56" s="1"/>
+      <c r="H56" s="1"/>
+      <c r="I56" s="1"/>
+      <c r="J56" s="1"/>
+      <c r="K56" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="44">
-    <mergeCell ref="A67:C67"/>
-    <mergeCell ref="E67:J67"/>
-    <mergeCell ref="A69:J69"/>
-    <mergeCell ref="A70:J70"/>
-    <mergeCell ref="A62:J62"/>
-    <mergeCell ref="A63:J63"/>
-    <mergeCell ref="A65:J65"/>
-    <mergeCell ref="A66:C66"/>
-    <mergeCell ref="E66:J66"/>
-    <mergeCell ref="A55:J55"/>
-    <mergeCell ref="A56:J56"/>
-    <mergeCell ref="A58:J58"/>
-    <mergeCell ref="A59:J59"/>
-    <mergeCell ref="A60:J60"/>
-    <mergeCell ref="A48:J48"/>
-    <mergeCell ref="A50:J50"/>
-    <mergeCell ref="A51:J51"/>
-    <mergeCell ref="A52:J52"/>
-    <mergeCell ref="A54:J54"/>
-    <mergeCell ref="A41:J41"/>
-    <mergeCell ref="A43:J43"/>
-    <mergeCell ref="A44:J44"/>
-    <mergeCell ref="A46:J46"/>
-    <mergeCell ref="A47:J47"/>
-    <mergeCell ref="A30:C30"/>
-    <mergeCell ref="A31:C31"/>
-    <mergeCell ref="A32:C32"/>
-    <mergeCell ref="A34:D35"/>
-    <mergeCell ref="A37:D39"/>
-    <mergeCell ref="A13:J13"/>
-    <mergeCell ref="A14:J14"/>
-    <mergeCell ref="A27:J27"/>
-    <mergeCell ref="A28:C28"/>
-    <mergeCell ref="A29:C29"/>
-    <mergeCell ref="A8:J8"/>
-    <mergeCell ref="A9:J9"/>
-    <mergeCell ref="A10:J10"/>
-    <mergeCell ref="A11:J11"/>
-    <mergeCell ref="A12:H12"/>
-    <mergeCell ref="E2:H3"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="C6:F6"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="M27:V27"/>
+    <mergeCell ref="M28:V30"/>
+    <mergeCell ref="B11:K12"/>
+    <mergeCell ref="B13:I13"/>
+    <mergeCell ref="M16:V18"/>
+    <mergeCell ref="M20:V20"/>
+    <mergeCell ref="M21:V21"/>
+    <mergeCell ref="M22:V24"/>
+    <mergeCell ref="M26:V26"/>
+    <mergeCell ref="M7:V7"/>
+    <mergeCell ref="M9:V9"/>
+    <mergeCell ref="M10:V12"/>
+    <mergeCell ref="M14:V14"/>
+    <mergeCell ref="M15:V15"/>
+    <mergeCell ref="M32:V32"/>
+    <mergeCell ref="M33:V33"/>
+    <mergeCell ref="M34:V36"/>
+    <mergeCell ref="M38:V38"/>
+    <mergeCell ref="M39:V39"/>
+    <mergeCell ref="B47:D47"/>
+    <mergeCell ref="F47:K47"/>
+    <mergeCell ref="B49:K49"/>
+    <mergeCell ref="B50:K50"/>
+    <mergeCell ref="B45:K45"/>
+    <mergeCell ref="B46:D46"/>
+    <mergeCell ref="F46:K46"/>
+    <mergeCell ref="B42:K42"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="B33:D33"/>
+    <mergeCell ref="B35:E36"/>
+    <mergeCell ref="B38:E40"/>
+    <mergeCell ref="B14:K14"/>
+    <mergeCell ref="B15:K15"/>
+    <mergeCell ref="B28:K28"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="B9:K9"/>
+    <mergeCell ref="B10:K10"/>
+    <mergeCell ref="F3:I4"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="D7:G7"/>
+    <mergeCell ref="H7:I7"/>
+    <mergeCell ref="J7:K7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
